--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_1.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_1.xlsx
@@ -463,55 +463,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[1, 2, 8, 6, 2]</t>
+          <t>[3, 6, 8, 5, 6]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9607498138928505</v>
+        <v>0.9523974033148742</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9607498138928505</v>
+        <v>0.9523974033148742</v>
       </c>
       <c r="E2" t="n">
-        <v>97.71000000000001</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>79.02999999999999</v>
+        <v>60.41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[8, 9, 7, 7, 9]</t>
+          <t>[4, 5, 8, 5, 9]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9279523291066274</v>
+        <v>0.9699773134284181</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9279523291066274</v>
+        <v>0.9699773134284181</v>
       </c>
       <c r="E3" t="n">
-        <v>95.64999999999999</v>
+        <v>98.28</v>
       </c>
       <c r="F3" t="n">
-        <v>63.69</v>
+        <v>76.28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[6, 5, 6, 3, 9]</t>
+          <t>[6, 2, 7, 0, 5]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,22 +520,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9487738139162639</v>
+        <v>0.9581353575295181</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9487738139162639</v>
+        <v>0.9581353575295181</v>
       </c>
       <c r="E4" t="n">
-        <v>87.83999999999999</v>
+        <v>84.88999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>71.52</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[5, 6, 0, 3, 1]</t>
+          <t>[6, 3, 9, 3, 0]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -544,46 +544,46 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9611593259101519</v>
+        <v>0.9548197679239597</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9611593259101519</v>
+        <v>0.9548197679239597</v>
       </c>
       <c r="E5" t="n">
-        <v>92.51000000000001</v>
+        <v>75.91999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>68.90000000000001</v>
+        <v>64.74000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[0, 4, 1, 4, 6]</t>
+          <t>[5, 0, 5, 9, 5]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9667360809967936</v>
+        <v>0.9770654009356525</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9667360809967936</v>
+        <v>0.9770654009356525</v>
       </c>
       <c r="E6" t="n">
-        <v>85.09</v>
+        <v>96.53999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>77.16999999999999</v>
+        <v>75.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[3, 0, 1, 0, 5]</t>
+          <t>[1, 2, 3, 6, 4]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -592,22 +592,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9709434894531578</v>
+        <v>0.964594154363864</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9709434894531578</v>
+        <v>0.964594154363864</v>
       </c>
       <c r="E7" t="n">
-        <v>94.92999999999999</v>
+        <v>85.86000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>67.8</v>
+        <v>71.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[1, 5, 3, 7, 5]</t>
+          <t>[2, 3, 2, 0, 5]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -616,22 +616,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9584787910904871</v>
+        <v>0.9716342433057984</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9584787910904871</v>
+        <v>0.9716342433057984</v>
       </c>
       <c r="E8" t="n">
-        <v>99.74999999999999</v>
+        <v>79.19999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>65.12</v>
+        <v>73.80000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[9, 3, 4, 6, 7]</t>
+          <t>[2, 5, 2, 5, 7]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,142 +640,142 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9481406589829385</v>
+        <v>0.9632990057695925</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9481406589829385</v>
+        <v>0.9632990057695925</v>
       </c>
       <c r="E9" t="n">
-        <v>90.41</v>
+        <v>88.19</v>
       </c>
       <c r="F9" t="n">
-        <v>69.63</v>
+        <v>71.45999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[5, 9, 6, 7, 8]</t>
+          <t>[2, 5, 1, 3, 4]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9359629751020949</v>
+        <v>0.9826783453666755</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9359629751020949</v>
+        <v>0.9826783453666755</v>
       </c>
       <c r="E10" t="n">
-        <v>90.95999999999999</v>
+        <v>97.47999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>72.43000000000001</v>
+        <v>79.61999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[5, 3, 4, 6, 7]</t>
+          <t>[3, 0, 4, 5, 7]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.956675359706428</v>
+        <v>0.9814294831002998</v>
       </c>
       <c r="D11" t="n">
-        <v>0.956675359706428</v>
+        <v>0.9814294831002998</v>
       </c>
       <c r="E11" t="n">
-        <v>90.75999999999999</v>
+        <v>87.97</v>
       </c>
       <c r="F11" t="n">
-        <v>74.52</v>
+        <v>76.42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[2, 7, 2, 0, 3]</t>
+          <t>[3, 1, 6, 5, 0]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.964401304508817</v>
+        <v>0.9799668354884064</v>
       </c>
       <c r="D12" t="n">
-        <v>0.964401304508817</v>
+        <v>0.9799668354884064</v>
       </c>
       <c r="E12" t="n">
-        <v>86.27000000000001</v>
+        <v>97.72</v>
       </c>
       <c r="F12" t="n">
-        <v>64.5</v>
+        <v>76.17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[8, 8, 0, 9, 7]</t>
+          <t>[0, 9, 9, 6, 3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9402010030092836</v>
+        <v>0.9533258647742587</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9402010030092836</v>
+        <v>0.9533258647742587</v>
       </c>
       <c r="E13" t="n">
-        <v>93.94</v>
+        <v>94.25999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>71.73999999999999</v>
+        <v>79.69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[2, 1, 2, 2, 4]</t>
+          <t>[7, 4, 1, 3, 5]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9837064748423342</v>
+        <v>0.9771830383630976</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9837064748423342</v>
+        <v>0.9771830383630976</v>
       </c>
       <c r="E14" t="n">
-        <v>94.61</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>76.06999999999999</v>
+        <v>75.13000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[1, 5, 9, 2, 2]</t>
+          <t>[2, 2, 6, 5, 1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -784,70 +784,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9582037772498666</v>
+        <v>0.9624596653297682</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9582037772498666</v>
+        <v>0.9624596653297682</v>
       </c>
       <c r="E15" t="n">
-        <v>87.11999999999999</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>60.44</v>
+        <v>75.53</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[9, 3, 1, 6, 6]</t>
+          <t>[4, 9, 3, 6, 5]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9516153786570758</v>
+        <v>0.9551557185041716</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9516153786570758</v>
+        <v>0.9551557185041716</v>
       </c>
       <c r="E16" t="n">
-        <v>89.74000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="F16" t="n">
-        <v>65.11</v>
+        <v>74.88</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[3, 0, 8, 5, 9]</t>
+          <t>[5, 0, 9, 9, 5]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9582403326764044</v>
+        <v>0.9569262997221641</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9582403326764044</v>
+        <v>0.9569262997221641</v>
       </c>
       <c r="E17" t="n">
-        <v>95.44</v>
+        <v>98.66</v>
       </c>
       <c r="F17" t="n">
-        <v>69.8</v>
+        <v>79.31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[2, 6, 0, 7, 0]</t>
+          <t>[1, 3, 8, 1, 2]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -856,22 +856,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9549115105596512</v>
+        <v>0.9640165273457677</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9549115105596512</v>
+        <v>0.9640165273457677</v>
       </c>
       <c r="E18" t="n">
-        <v>81.66</v>
+        <v>97.88</v>
       </c>
       <c r="F18" t="n">
-        <v>73.29000000000001</v>
+        <v>72.61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[2, 2, 9, 3, 2]</t>
+          <t>[5, 3, 4, 4, 2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.960323291582588</v>
+        <v>0.9618526935250277</v>
       </c>
       <c r="D19" t="n">
-        <v>0.960323291582588</v>
+        <v>0.9618526935250277</v>
       </c>
       <c r="E19" t="n">
-        <v>83.01000000000001</v>
+        <v>73.02</v>
       </c>
       <c r="F19" t="n">
-        <v>59.02</v>
+        <v>69.31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[1, 0, 5, 5, 8]</t>
+          <t>[3, 3, 6, 4, 8]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -904,22 +904,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9644914486725087</v>
+        <v>0.960373387449493</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9644914486725087</v>
+        <v>0.960373387449493</v>
       </c>
       <c r="E20" t="n">
-        <v>95.20999999999999</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>72.63</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[8, 9, 8, 2, 6]</t>
+          <t>[3, 5, 9, 3, 5]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -928,94 +928,94 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9411725462173361</v>
+        <v>0.958730815415591</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9411725462173361</v>
+        <v>0.958730815415591</v>
       </c>
       <c r="E21" t="n">
-        <v>86.41</v>
+        <v>77.22</v>
       </c>
       <c r="F21" t="n">
-        <v>72.17999999999999</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[7, 9, 3, 8, 8]</t>
+          <t>[5, 7, 4, 9, 5]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9388059280666959</v>
+        <v>0.9517535033487842</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9388059280666959</v>
+        <v>0.9517535033487842</v>
       </c>
       <c r="E22" t="n">
-        <v>98.61999999999999</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>67.45999999999999</v>
+        <v>76.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[8, 6, 0, 7, 7]</t>
+          <t>[3, 1, 6, 3, 4]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.945658847802238</v>
+        <v>0.9769155271691523</v>
       </c>
       <c r="D23" t="n">
-        <v>0.945658847802238</v>
+        <v>0.9769155271691523</v>
       </c>
       <c r="E23" t="n">
-        <v>89.53</v>
+        <v>94.08000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>74.43000000000001</v>
+        <v>73.67999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[0, 0, 4, 5, 9]</t>
+          <t>[4, 7, 0, 3, 6]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9653747935565081</v>
+        <v>0.9809893615001967</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9653747935565081</v>
+        <v>0.9809893615001967</v>
       </c>
       <c r="E24" t="n">
-        <v>87.72999999999999</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>75.63</v>
+        <v>78.56</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[5, 6, 8, 9, 0]</t>
+          <t>[6, 1, 2, 9, 3]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1024,22 +1024,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9387543724567066</v>
+        <v>0.9577192681246145</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9387543724567066</v>
+        <v>0.9577192681246145</v>
       </c>
       <c r="E25" t="n">
-        <v>88.34</v>
+        <v>91.52</v>
       </c>
       <c r="F25" t="n">
-        <v>75.17999999999999</v>
+        <v>71.53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[6, 5, 5, 2, 1]</t>
+          <t>[4, 6, 8, 2, 9]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1048,70 +1048,70 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.957374269816062</v>
+        <v>0.9526582291620836</v>
       </c>
       <c r="D26" t="n">
-        <v>0.957374269816062</v>
+        <v>0.9526582291620836</v>
       </c>
       <c r="E26" t="n">
-        <v>87.53999999999999</v>
+        <v>85.66</v>
       </c>
       <c r="F26" t="n">
-        <v>69.84</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[7, 2, 7, 8, 0]</t>
+          <t>[8, 5, 4, 6, 9]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9463786535903156</v>
+        <v>0.9690284175724285</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9463786535903156</v>
+        <v>0.9690284175724285</v>
       </c>
       <c r="E27" t="n">
-        <v>89.46000000000001</v>
+        <v>99.88</v>
       </c>
       <c r="F27" t="n">
-        <v>69.92</v>
+        <v>78.41999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[1, 5, 7, 5, 5]</t>
+          <t>[8, 4, 3, 7, 5]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9569397782354329</v>
+        <v>0.9730221339904231</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9569397782354329</v>
+        <v>0.9730221339904231</v>
       </c>
       <c r="E28" t="n">
-        <v>97.26999999999998</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>69.47</v>
+        <v>78.35000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[9, 5, 1, 5, 0]</t>
+          <t>[9, 0, 8, 1, 3]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1120,22 +1120,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9548353207824625</v>
+        <v>0.9549183797167023</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9548353207824625</v>
+        <v>0.9549183797167023</v>
       </c>
       <c r="E29" t="n">
-        <v>94.29999999999998</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>67.33</v>
+        <v>70.78</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[3, 9, 4, 0, 7]</t>
+          <t>[4, 9, 3, 6, 1]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1144,46 +1144,46 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9573125890231585</v>
+        <v>0.9521846484629657</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9573125890231585</v>
+        <v>0.9521846484629657</v>
       </c>
       <c r="E30" t="n">
-        <v>92.82999999999998</v>
+        <v>85.98</v>
       </c>
       <c r="F30" t="n">
-        <v>68.53</v>
+        <v>68.65000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[4, 3, 9, 5, 2]</t>
+          <t>[9, 4, 0, 5, 3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9542664457403631</v>
+        <v>0.9774421601039998</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9542664457403631</v>
+        <v>0.9774421601039998</v>
       </c>
       <c r="E31" t="n">
-        <v>89.91999999999999</v>
+        <v>90</v>
       </c>
       <c r="F31" t="n">
-        <v>67.94</v>
+        <v>78.66999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[0, 0, 7, 0, 8]</t>
+          <t>[8, 1, 8, 5, 6]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1192,70 +1192,70 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9639195892763395</v>
+        <v>0.9500140165367299</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9639195892763395</v>
+        <v>0.9500140165367299</v>
       </c>
       <c r="E32" t="n">
-        <v>89.33</v>
+        <v>95.16</v>
       </c>
       <c r="F32" t="n">
-        <v>76.08</v>
+        <v>66.45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[5, 0, 2, 7, 0]</t>
+          <t>[3, 4, 7, 8, 3]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9615302625195906</v>
+        <v>0.957042338218082</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9615302625195906</v>
+        <v>0.957042338218082</v>
       </c>
       <c r="E33" t="n">
-        <v>86.28</v>
+        <v>90.25</v>
       </c>
       <c r="F33" t="n">
-        <v>72.26000000000001</v>
+        <v>72.27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[6, 5, 2, 2, 9]</t>
+          <t>[0, 3, 3, 7, 8]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9636426887548917</v>
+        <v>0.982067507504313</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9636426887548917</v>
+        <v>0.982067507504313</v>
       </c>
       <c r="E34" t="n">
-        <v>99.23999999999999</v>
+        <v>96.97999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>78.72999999999999</v>
+        <v>77.47</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[9, 9, 5, 7, 6]</t>
+          <t>[2, 4, 4, 6, 1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9319127921941837</v>
+        <v>0.9592448155306914</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9319127921941837</v>
+        <v>0.9592448155306914</v>
       </c>
       <c r="E35" t="n">
-        <v>90.05</v>
+        <v>85.31999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>67.13</v>
+        <v>76.97</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[3, 0, 8, 6, 1]</t>
+          <t>[5, 8, 3, 9, 3]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9570990269963365</v>
+        <v>0.9532157435112506</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9570990269963365</v>
+        <v>0.9532157435112506</v>
       </c>
       <c r="E36" t="n">
-        <v>93.07000000000001</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>69.31</v>
+        <v>69.32000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[0, 1, 6, 8, 9]</t>
+          <t>[6, 3, 6, 8, 3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9560603716108393</v>
+        <v>0.9724956152499596</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9560603716108393</v>
+        <v>0.9724956152499596</v>
       </c>
       <c r="E37" t="n">
-        <v>90.23999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="F37" t="n">
-        <v>68.77</v>
+        <v>72.53999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[7, 3, 1, 2, 9]</t>
+          <t>[3, 5, 6, 8, 4]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.961479441118115</v>
+        <v>0.9531513077949986</v>
       </c>
       <c r="D38" t="n">
-        <v>0.961479441118115</v>
+        <v>0.9531513077949986</v>
       </c>
       <c r="E38" t="n">
-        <v>94.70999999999999</v>
+        <v>78.53999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>56.75</v>
+        <v>62.59</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[0, 9, 6, 1, 1]</t>
+          <t>[9, 0, 6, 8, 9]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1360,22 +1360,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9550713524231975</v>
+        <v>0.9483197641591085</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9550713524231975</v>
+        <v>0.9483197641591085</v>
       </c>
       <c r="E39" t="n">
-        <v>91.58</v>
+        <v>86.42000000000002</v>
       </c>
       <c r="F39" t="n">
-        <v>61.95</v>
+        <v>73.23999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[2, 5, 4, 1, 0]</t>
+          <t>[5, 5, 5, 5, 7]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1384,46 +1384,46 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9666343593122678</v>
+        <v>0.9566436338311466</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9666343593122678</v>
+        <v>0.9566436338311466</v>
       </c>
       <c r="E40" t="n">
-        <v>87.49000000000001</v>
+        <v>84.19</v>
       </c>
       <c r="F40" t="n">
-        <v>70.7</v>
+        <v>57.06</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[5, 3, 6, 3, 6]</t>
+          <t>[9, 3, 1, 0, 3]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9573980264763786</v>
+        <v>0.9762716926703133</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9573980264763786</v>
+        <v>0.9762716926703133</v>
       </c>
       <c r="E41" t="n">
-        <v>90.66999999999999</v>
+        <v>95.24000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>72.06</v>
+        <v>77.22999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[5, 5, 3, 9, 6]</t>
+          <t>[3, 7, 1, 4, 7]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1432,22 +1432,22 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9504180244706204</v>
+        <v>0.9598333263204163</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9504180244706204</v>
+        <v>0.9598333263204163</v>
       </c>
       <c r="E42" t="n">
-        <v>92.46000000000001</v>
+        <v>88.44</v>
       </c>
       <c r="F42" t="n">
-        <v>70.49000000000001</v>
+        <v>67.84999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[1, 6, 1, 8, 8]</t>
+          <t>[9, 0, 7, 2, 8]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1456,22 +1456,22 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9531413618102931</v>
+        <v>0.9545914631161865</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9531413618102931</v>
+        <v>0.9545914631161865</v>
       </c>
       <c r="E43" t="n">
-        <v>95.25</v>
+        <v>87.78999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>67.72999999999999</v>
+        <v>76.92999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[5, 7, 0, 1, 2]</t>
+          <t>[8, 3, 9, 1, 7]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1480,22 +1480,22 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9618302291932393</v>
+        <v>0.9516612970294666</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9618302291932393</v>
+        <v>0.9516612970294666</v>
       </c>
       <c r="E44" t="n">
-        <v>90.38</v>
+        <v>93.39</v>
       </c>
       <c r="F44" t="n">
-        <v>65.92</v>
+        <v>67.56</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[1, 6, 2, 3, 7]</t>
+          <t>[0, 3, 5, 0, 7]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1504,22 +1504,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9623109883810991</v>
+        <v>0.9699271517948915</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9623109883810991</v>
+        <v>0.9699271517948915</v>
       </c>
       <c r="E45" t="n">
-        <v>90.44</v>
+        <v>75.39</v>
       </c>
       <c r="F45" t="n">
-        <v>62.67</v>
+        <v>68.03999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[9, 8, 7, 5, 0]</t>
+          <t>[0, 4, 5, 9, 0]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1528,22 +1528,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9377677130670137</v>
+        <v>0.9588701094177807</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9377677130670137</v>
+        <v>0.9588701094177807</v>
       </c>
       <c r="E46" t="n">
-        <v>93.38</v>
+        <v>73.88</v>
       </c>
       <c r="F46" t="n">
-        <v>71.33</v>
+        <v>74.61</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[4, 3, 8, 2, 6]</t>
+          <t>[9, 9, 5, 8, 6]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1552,22 +1552,22 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9591644041088289</v>
+        <v>0.9396830493091838</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9591644041088289</v>
+        <v>0.9396830493091838</v>
       </c>
       <c r="E47" t="n">
-        <v>86.20999999999999</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>74.27</v>
+        <v>67.31</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[4, 6, 9, 3, 9]</t>
+          <t>[7, 8, 3, 3, 9]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1576,88 +1576,88 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9472758008431283</v>
+        <v>0.9553689015372844</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9472758008431283</v>
+        <v>0.9553689015372844</v>
       </c>
       <c r="E48" t="n">
-        <v>89.64</v>
+        <v>82.69</v>
       </c>
       <c r="F48" t="n">
-        <v>67.56</v>
+        <v>62.04000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[8, 9, 3, 1, 6]</t>
+          <t>[8, 0, 0, 3, 3]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.951646063180224</v>
+        <v>0.969874210953435</v>
       </c>
       <c r="D49" t="n">
-        <v>0.951646063180224</v>
+        <v>0.969874210953435</v>
       </c>
       <c r="E49" t="n">
-        <v>94.92</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>64.48999999999999</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[1, 6, 9, 2, 7]</t>
+          <t>[4, 8, 5, 3, 6]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9524159469340949</v>
+        <v>0.9750137101160323</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9524159469340949</v>
+        <v>0.9750137101160323</v>
       </c>
       <c r="E50" t="n">
-        <v>87.61</v>
+        <v>91.75999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>62.13</v>
+        <v>72.58</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[4, 4, 4, 1, 2]</t>
+          <t>[8, 5, 4, 8, 5]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9657686963820594</v>
+        <v>0.9695606250335916</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9657686963820594</v>
+        <v>0.9695606250335916</v>
       </c>
       <c r="E51" t="n">
-        <v>84.75</v>
+        <v>98.53999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>74.69</v>
+        <v>74.86</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_1.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_1.xlsx
@@ -463,55 +463,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[3, 6, 8, 5, 6]</t>
+          <t>[0, 0, 8, 4, 8]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9523974033148742</v>
+        <v>0.9789526051370631</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9523974033148742</v>
+        <v>0.9789526051370631</v>
       </c>
       <c r="E2" t="n">
-        <v>83.68000000000001</v>
+        <v>87.58</v>
       </c>
       <c r="F2" t="n">
-        <v>60.41</v>
+        <v>76.19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[4, 5, 8, 5, 9]</t>
+          <t>[1, 8, 8, 1, 0]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9699773134284181</v>
+        <v>0.9776898360181028</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9699773134284181</v>
+        <v>0.9776898360181028</v>
       </c>
       <c r="E3" t="n">
-        <v>98.28</v>
+        <v>90.38</v>
       </c>
       <c r="F3" t="n">
-        <v>76.28</v>
+        <v>64.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[6, 2, 7, 0, 5]</t>
+          <t>[9, 3, 7, 9, 8]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,358 +520,358 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9581353575295181</v>
+        <v>0.9477858230279925</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9581353575295181</v>
+        <v>0.9477858230279925</v>
       </c>
       <c r="E4" t="n">
-        <v>84.88999999999999</v>
+        <v>83.03</v>
       </c>
       <c r="F4" t="n">
-        <v>72.33</v>
+        <v>66.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[6, 3, 9, 3, 0]</t>
+          <t>[7, 2, 3, 5, 6]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9548197679239597</v>
+        <v>0.9767567480369879</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9548197679239597</v>
+        <v>0.9767567480369879</v>
       </c>
       <c r="E5" t="n">
-        <v>75.91999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>64.74000000000001</v>
+        <v>79.96000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[5, 0, 5, 9, 5]</t>
+          <t>[0, 1, 0, 1, 4]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9770654009356525</v>
+        <v>0.9845708526076199</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9770654009356525</v>
+        <v>0.9845708526076199</v>
       </c>
       <c r="E6" t="n">
-        <v>96.53999999999999</v>
+        <v>96.02</v>
       </c>
       <c r="F6" t="n">
-        <v>75.23</v>
+        <v>76.11999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 6, 4]</t>
+          <t>[6, 8, 5, 2, 8]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.964594154363864</v>
+        <v>0.9750955043375055</v>
       </c>
       <c r="D7" t="n">
-        <v>0.964594154363864</v>
+        <v>0.9750955043375055</v>
       </c>
       <c r="E7" t="n">
-        <v>85.86000000000001</v>
+        <v>90.86</v>
       </c>
       <c r="F7" t="n">
-        <v>71.77</v>
+        <v>71.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[2, 3, 2, 0, 5]</t>
+          <t>[6, 3, 9, 5, 9]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9716342433057984</v>
+        <v>0.9694035219680313</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9716342433057984</v>
+        <v>0.9694035219680313</v>
       </c>
       <c r="E8" t="n">
-        <v>79.19999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>73.80000000000001</v>
+        <v>77.53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[2, 5, 2, 5, 7]</t>
+          <t>[5, 1, 3, 7, 5]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9632990057695925</v>
+        <v>0.9779381972281564</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9632990057695925</v>
+        <v>0.9779381972281564</v>
       </c>
       <c r="E9" t="n">
-        <v>88.19</v>
+        <v>86.31</v>
       </c>
       <c r="F9" t="n">
-        <v>71.45999999999999</v>
+        <v>74.50999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[2, 5, 1, 3, 4]</t>
+          <t>[4, 5, 5, 6, 9]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9826783453666755</v>
+        <v>0.9562577839526032</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9826783453666755</v>
+        <v>0.9562577839526032</v>
       </c>
       <c r="E10" t="n">
-        <v>97.47999999999999</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>79.61999999999999</v>
+        <v>66.42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[3, 0, 4, 5, 7]</t>
+          <t>[1, 2, 6, 0, 5]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9814294831002998</v>
+        <v>0.9699355382564967</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9814294831002998</v>
+        <v>0.9699355382564967</v>
       </c>
       <c r="E11" t="n">
-        <v>87.97</v>
+        <v>92.64</v>
       </c>
       <c r="F11" t="n">
-        <v>76.42</v>
+        <v>75.93000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[3, 1, 6, 5, 0]</t>
+          <t>[3, 8, 8, 4, 8]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9799668354884064</v>
+        <v>0.9563707471068276</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9799668354884064</v>
+        <v>0.9563707471068276</v>
       </c>
       <c r="E12" t="n">
-        <v>97.72</v>
+        <v>77.84</v>
       </c>
       <c r="F12" t="n">
-        <v>76.17</v>
+        <v>56.81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[0, 9, 9, 6, 3]</t>
+          <t>[0, 8, 5, 7, 5]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9533258647742587</v>
+        <v>0.9721139865579286</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9533258647742587</v>
+        <v>0.9721139865579286</v>
       </c>
       <c r="E13" t="n">
-        <v>94.25999999999999</v>
+        <v>80.83000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>79.69</v>
+        <v>73.44999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[7, 4, 1, 3, 5]</t>
+          <t>[8, 5, 0, 5, 8]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9771830383630976</v>
+        <v>0.9761503839495406</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9771830383630976</v>
+        <v>0.9761503839495406</v>
       </c>
       <c r="E14" t="n">
-        <v>98.56999999999999</v>
+        <v>96.49000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>75.13000000000001</v>
+        <v>73.92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[2, 2, 6, 5, 1]</t>
+          <t>[5, 5, 3, 3, 8]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9624596653297682</v>
+        <v>0.9640636599772741</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9624596653297682</v>
+        <v>0.9640636599772741</v>
       </c>
       <c r="E15" t="n">
-        <v>94.39999999999999</v>
+        <v>99.21000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>75.53</v>
+        <v>75.64</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[4, 9, 3, 6, 5]</t>
+          <t>[6, 5, 0, 1, 2]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9551557185041716</v>
+        <v>0.9646923298577599</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9551557185041716</v>
+        <v>0.9646923298577599</v>
       </c>
       <c r="E16" t="n">
-        <v>94.5</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>74.88</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[5, 0, 9, 9, 5]</t>
+          <t>[8, 3, 3, 4, 3]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9569262997221641</v>
+        <v>0.9615482992488961</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9569262997221641</v>
+        <v>0.9615482992488961</v>
       </c>
       <c r="E17" t="n">
-        <v>98.66</v>
+        <v>79.38</v>
       </c>
       <c r="F17" t="n">
-        <v>79.31</v>
+        <v>62.89000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[1, 3, 8, 1, 2]</t>
+          <t>[4, 5, 3, 8, 3]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9640165273457677</v>
+        <v>0.9732147792775706</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9640165273457677</v>
+        <v>0.9732147792775706</v>
       </c>
       <c r="E18" t="n">
-        <v>97.88</v>
+        <v>93.09</v>
       </c>
       <c r="F18" t="n">
-        <v>72.61</v>
+        <v>74.31999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[5, 3, 4, 4, 2]</t>
+          <t>[5, 0, 7, 1, 8]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -880,70 +880,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9618526935250277</v>
+        <v>0.9622104478632564</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9618526935250277</v>
+        <v>0.9622104478632564</v>
       </c>
       <c r="E19" t="n">
-        <v>73.02</v>
+        <v>69.88</v>
       </c>
       <c r="F19" t="n">
-        <v>69.31</v>
+        <v>61.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[3, 3, 6, 4, 8]</t>
+          <t>[3, 9, 6, 5, 7]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.960373387449493</v>
+        <v>0.9747580769793297</v>
       </c>
       <c r="D20" t="n">
-        <v>0.960373387449493</v>
+        <v>0.9747580769793297</v>
       </c>
       <c r="E20" t="n">
-        <v>75.54000000000001</v>
+        <v>88.88000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>61.71</v>
+        <v>78.51000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[3, 5, 9, 3, 5]</t>
+          <t>[5, 5, 2, 8, 7]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.958730815415591</v>
+        <v>0.9724036488206499</v>
       </c>
       <c r="D21" t="n">
-        <v>0.958730815415591</v>
+        <v>0.9724036488206499</v>
       </c>
       <c r="E21" t="n">
-        <v>77.22</v>
+        <v>99.67</v>
       </c>
       <c r="F21" t="n">
-        <v>56.67</v>
+        <v>79.60000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[5, 7, 4, 9, 5]</t>
+          <t>[5, 6, 2, 3, 8]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -952,190 +952,190 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9517535033487842</v>
+        <v>0.9642955499890962</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9517535033487842</v>
+        <v>0.9642955499890962</v>
       </c>
       <c r="E22" t="n">
-        <v>98.98999999999999</v>
+        <v>92.50999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>76.33</v>
+        <v>71.09</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[3, 1, 6, 3, 4]</t>
+          <t>[7, 1, 6, 9, 7]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9769155271691523</v>
+        <v>0.9544991660199619</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9769155271691523</v>
+        <v>0.9544991660199619</v>
       </c>
       <c r="E23" t="n">
-        <v>94.08000000000001</v>
+        <v>75.89</v>
       </c>
       <c r="F23" t="n">
-        <v>73.67999999999999</v>
+        <v>70.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[4, 7, 0, 3, 6]</t>
+          <t>[3, 8, 3, 6, 9]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9809893615001967</v>
+        <v>0.9570090056379446</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9809893615001967</v>
+        <v>0.9570090056379446</v>
       </c>
       <c r="E24" t="n">
-        <v>89.56999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="F24" t="n">
-        <v>78.56</v>
+        <v>61.25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[6, 1, 2, 9, 3]</t>
+          <t>[5, 5, 2, 3, 6]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9577192681246145</v>
+        <v>0.9770779171539705</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9577192681246145</v>
+        <v>0.9770779171539705</v>
       </c>
       <c r="E25" t="n">
-        <v>91.52</v>
+        <v>91.83</v>
       </c>
       <c r="F25" t="n">
-        <v>71.53</v>
+        <v>75.27000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[4, 6, 8, 2, 9]</t>
+          <t>[7, 5, 1, 9, 1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9526582291620836</v>
+        <v>0.9706359444474971</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9526582291620836</v>
+        <v>0.9706359444474971</v>
       </c>
       <c r="E26" t="n">
-        <v>85.66</v>
+        <v>96.59</v>
       </c>
       <c r="F26" t="n">
-        <v>74.75</v>
+        <v>74.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[8, 5, 4, 6, 9]</t>
+          <t>[1, 4, 4, 0, 0]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9690284175724285</v>
+        <v>0.9693546485876188</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9690284175724285</v>
+        <v>0.9693546485876188</v>
       </c>
       <c r="E27" t="n">
-        <v>99.88</v>
+        <v>83.95000000000002</v>
       </c>
       <c r="F27" t="n">
-        <v>78.41999999999999</v>
+        <v>70.99000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[8, 4, 3, 7, 5]</t>
+          <t>[0, 4, 1, 4, 8]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9730221339904231</v>
+        <v>0.9711139749195544</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9730221339904231</v>
+        <v>0.9711139749195544</v>
       </c>
       <c r="E28" t="n">
-        <v>92.70999999999999</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>78.35000000000001</v>
+        <v>75.97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[9, 0, 8, 1, 3]</t>
+          <t>[5, 3, 8, 0, 5]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9549183797167023</v>
+        <v>0.9735349341338189</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9549183797167023</v>
+        <v>0.9735349341338189</v>
       </c>
       <c r="E29" t="n">
-        <v>87.40000000000001</v>
+        <v>83.98000000000002</v>
       </c>
       <c r="F29" t="n">
-        <v>70.78</v>
+        <v>70.66</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[4, 9, 3, 6, 1]</t>
+          <t>[1, 0, 2, 3, 5]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1144,190 +1144,190 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9521846484629657</v>
+        <v>0.9695999554428285</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9521846484629657</v>
+        <v>0.9695999554428285</v>
       </c>
       <c r="E30" t="n">
-        <v>85.98</v>
+        <v>80.58000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>68.65000000000001</v>
+        <v>63.92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[9, 4, 0, 5, 3]</t>
+          <t>[8, 9, 7, 6, 1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9774421601039998</v>
+        <v>0.9699756418559842</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9774421601039998</v>
+        <v>0.9699756418559842</v>
       </c>
       <c r="E31" t="n">
-        <v>90</v>
+        <v>97.85000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>78.66999999999999</v>
+        <v>77.57000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[8, 1, 8, 5, 6]</t>
+          <t>[1, 1, 0, 7, 3]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9500140165367299</v>
+        <v>0.9702172427365852</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9500140165367299</v>
+        <v>0.9702172427365852</v>
       </c>
       <c r="E32" t="n">
-        <v>95.16</v>
+        <v>88.22999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>66.45</v>
+        <v>76.12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[3, 4, 7, 8, 3]</t>
+          <t>[3, 0, 8, 3, 4]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.957042338218082</v>
+        <v>0.9765797535112294</v>
       </c>
       <c r="D33" t="n">
-        <v>0.957042338218082</v>
+        <v>0.9765797535112294</v>
       </c>
       <c r="E33" t="n">
-        <v>90.25</v>
+        <v>92.25</v>
       </c>
       <c r="F33" t="n">
-        <v>72.27</v>
+        <v>76.59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[0, 3, 3, 7, 8]</t>
+          <t>[2, 1, 1, 3, 3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.982067507504313</v>
+        <v>0.969678486663636</v>
       </c>
       <c r="D34" t="n">
-        <v>0.982067507504313</v>
+        <v>0.969678486663636</v>
       </c>
       <c r="E34" t="n">
-        <v>96.97999999999999</v>
+        <v>85.28999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>77.47</v>
+        <v>61.94</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[2, 4, 4, 6, 1]</t>
+          <t>[7, 8, 8, 6, 8]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9592448155306914</v>
+        <v>0.9752956729656572</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9592448155306914</v>
+        <v>0.9752956729656572</v>
       </c>
       <c r="E35" t="n">
-        <v>85.31999999999999</v>
+        <v>95.32000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>76.97</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[5, 8, 3, 9, 3]</t>
+          <t>[6, 5, 7, 6, 3]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9532157435112506</v>
+        <v>0.9539171446683603</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9532157435112506</v>
+        <v>0.9539171446683603</v>
       </c>
       <c r="E36" t="n">
-        <v>92.81999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>69.32000000000001</v>
+        <v>65.85000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[6, 3, 6, 8, 3]</t>
+          <t>[5, 8, 2, 5, 6]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9724956152499596</v>
+        <v>0.9765032941618885</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9724956152499596</v>
+        <v>0.9765032941618885</v>
       </c>
       <c r="E37" t="n">
-        <v>98.5</v>
+        <v>91.40000000000002</v>
       </c>
       <c r="F37" t="n">
-        <v>72.53999999999999</v>
+        <v>70.14</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[3, 5, 6, 8, 4]</t>
+          <t>[0, 3, 8, 3, 0]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9531513077949986</v>
+        <v>0.9642525264564231</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9531513077949986</v>
+        <v>0.9642525264564231</v>
       </c>
       <c r="E38" t="n">
-        <v>78.53999999999999</v>
+        <v>69.42999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>62.59</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[9, 0, 6, 8, 9]</t>
+          <t>[2, 4, 6, 7, 6]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1360,22 +1360,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9483197641591085</v>
+        <v>0.9603798499328566</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9483197641591085</v>
+        <v>0.9603798499328566</v>
       </c>
       <c r="E39" t="n">
-        <v>86.42000000000002</v>
+        <v>82.7</v>
       </c>
       <c r="F39" t="n">
-        <v>73.23999999999999</v>
+        <v>74.09</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[5, 5, 5, 5, 7]</t>
+          <t>[3, 2, 1, 2, 6]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1384,94 +1384,94 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9566436338311466</v>
+        <v>0.9686165165707902</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9566436338311466</v>
+        <v>0.9686165165707902</v>
       </c>
       <c r="E40" t="n">
-        <v>84.19</v>
+        <v>89.88000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>57.06</v>
+        <v>67.39000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[9, 3, 1, 0, 3]</t>
+          <t>[4, 6, 3, 5, 8]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9762716926703133</v>
+        <v>0.9744266241392695</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9762716926703133</v>
+        <v>0.9744266241392695</v>
       </c>
       <c r="E41" t="n">
-        <v>95.24000000000001</v>
+        <v>91.44</v>
       </c>
       <c r="F41" t="n">
-        <v>77.22999999999999</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[3, 7, 1, 4, 7]</t>
+          <t>[9, 9, 0, 0, 8]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9598333263204163</v>
+        <v>0.975965738437965</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9598333263204163</v>
+        <v>0.975965738437965</v>
       </c>
       <c r="E42" t="n">
-        <v>88.44</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>67.84999999999999</v>
+        <v>78.82000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[9, 0, 7, 2, 8]</t>
+          <t>[6, 0, 4, 1, 3]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9545914631161865</v>
+        <v>0.9785893112396209</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9545914631161865</v>
+        <v>0.9785893112396209</v>
       </c>
       <c r="E43" t="n">
-        <v>87.78999999999999</v>
+        <v>94.66999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>76.92999999999999</v>
+        <v>76.98999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[8, 3, 9, 1, 7]</t>
+          <t>[1, 5, 3, 4, 3]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1480,22 +1480,22 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9516612970294666</v>
+        <v>0.9647259421224429</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9516612970294666</v>
+        <v>0.9647259421224429</v>
       </c>
       <c r="E44" t="n">
-        <v>93.39</v>
+        <v>80.69</v>
       </c>
       <c r="F44" t="n">
-        <v>67.56</v>
+        <v>63.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[0, 3, 5, 0, 7]</t>
+          <t>[0, 4, 2, 8, 1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1504,22 +1504,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9699271517948915</v>
+        <v>0.964514047604531</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9699271517948915</v>
+        <v>0.964514047604531</v>
       </c>
       <c r="E45" t="n">
-        <v>75.39</v>
+        <v>86.97</v>
       </c>
       <c r="F45" t="n">
-        <v>68.03999999999999</v>
+        <v>65.86</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[0, 4, 5, 9, 0]</t>
+          <t>[9, 0, 9, 6, 5]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1528,136 +1528,136 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9588701094177807</v>
+        <v>0.9498942026705512</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9588701094177807</v>
+        <v>0.9498942026705512</v>
       </c>
       <c r="E46" t="n">
-        <v>73.88</v>
+        <v>81.13</v>
       </c>
       <c r="F46" t="n">
-        <v>74.61</v>
+        <v>66.47</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[9, 9, 5, 8, 6]</t>
+          <t>[6, 4, 3, 5, 1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9396830493091838</v>
+        <v>0.9773796472219918</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9396830493091838</v>
+        <v>0.9773796472219918</v>
       </c>
       <c r="E47" t="n">
-        <v>89.31999999999999</v>
+        <v>93.86</v>
       </c>
       <c r="F47" t="n">
-        <v>67.31</v>
+        <v>76.33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[7, 8, 3, 3, 9]</t>
+          <t>[9, 1, 8, 9, 6]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9553689015372844</v>
+        <v>0.9722054543577252</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9553689015372844</v>
+        <v>0.9722054543577252</v>
       </c>
       <c r="E48" t="n">
-        <v>82.69</v>
+        <v>99.11999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>62.04000000000001</v>
+        <v>70.78999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[8, 0, 0, 3, 3]</t>
+          <t>[8, 1, 0, 1, 6]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.969874210953435</v>
+        <v>0.9664007748475051</v>
       </c>
       <c r="D49" t="n">
-        <v>0.969874210953435</v>
+        <v>0.9664007748475051</v>
       </c>
       <c r="E49" t="n">
-        <v>84.90000000000001</v>
+        <v>73.03</v>
       </c>
       <c r="F49" t="n">
-        <v>77.09999999999999</v>
+        <v>57.54</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[4, 8, 5, 3, 6]</t>
+          <t>[4, 5, 2, 7, 1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9750137101160323</v>
+        <v>0.9608496435463989</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9750137101160323</v>
+        <v>0.9608496435463989</v>
       </c>
       <c r="E50" t="n">
-        <v>91.75999999999999</v>
+        <v>86.53999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>72.58</v>
+        <v>70.37</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[8, 5, 4, 8, 5]</t>
+          <t>[0, 5, 3, 0, 3]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9695606250335916</v>
+        <v>0.9821331141516636</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9695606250335916</v>
+        <v>0.9821331141516636</v>
       </c>
       <c r="E51" t="n">
-        <v>98.53999999999999</v>
+        <v>81.96000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>74.86</v>
+        <v>77.28999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_1.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_1.xlsx
@@ -463,55 +463,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[0, 0, 8, 4, 8]</t>
+          <t>[4, 5, 5, 3, 5]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9789526051370631</v>
+        <v>0.9759671924549167</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9789526051370631</v>
+        <v>0.9759671924549167</v>
       </c>
       <c r="E2" t="n">
-        <v>87.58</v>
+        <v>93.78999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>76.19</v>
+        <v>76.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[1, 8, 8, 1, 0]</t>
+          <t>[5, 7, 4, 9, 7]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9776898360181028</v>
+        <v>0.9417537336538638</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9776898360181028</v>
+        <v>0.9417537336538638</v>
       </c>
       <c r="E3" t="n">
-        <v>90.38</v>
+        <v>78.53</v>
       </c>
       <c r="F3" t="n">
-        <v>64.69</v>
+        <v>75.23999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[9, 3, 7, 9, 8]</t>
+          <t>[8, 6, 0, 2, 9]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,118 +520,118 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9477858230279925</v>
+        <v>0.9577060555562528</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9477858230279925</v>
+        <v>0.9577060555562528</v>
       </c>
       <c r="E4" t="n">
-        <v>83.03</v>
+        <v>89.08999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>66.22</v>
+        <v>66.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[7, 2, 3, 5, 6]</t>
+          <t>[0, 6, 7, 3, 3]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9767567480369879</v>
+        <v>0.9749021815669767</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9767567480369879</v>
+        <v>0.9749021815669767</v>
       </c>
       <c r="E5" t="n">
-        <v>90.90000000000001</v>
+        <v>88.92</v>
       </c>
       <c r="F5" t="n">
-        <v>79.96000000000001</v>
+        <v>76.21000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[0, 1, 0, 1, 4]</t>
+          <t>[9, 6, 7, 7, 8]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9845708526076199</v>
+        <v>0.9312893881483579</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9845708526076199</v>
+        <v>0.9312893881483579</v>
       </c>
       <c r="E6" t="n">
-        <v>96.02</v>
+        <v>71.94999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>76.11999999999999</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[6, 8, 5, 2, 8]</t>
+          <t>[3, 0, 3, 5, 8]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9750955043375055</v>
+        <v>0.9810005391556259</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9750955043375055</v>
+        <v>0.9810005391556259</v>
       </c>
       <c r="E7" t="n">
-        <v>90.86</v>
+        <v>99.66</v>
       </c>
       <c r="F7" t="n">
-        <v>71.67</v>
+        <v>69.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[6, 3, 9, 5, 9]</t>
+          <t>[2, 2, 3, 7, 0]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9694035219680313</v>
+        <v>0.977010846837901</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9694035219680313</v>
+        <v>0.977010846837901</v>
       </c>
       <c r="E8" t="n">
-        <v>97.90000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="F8" t="n">
-        <v>77.53</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[5, 1, 3, 7, 5]</t>
+          <t>[7, 3, 1, 7, 9]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9779381972281564</v>
+        <v>0.9718673545344549</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9779381972281564</v>
+        <v>0.9718673545344549</v>
       </c>
       <c r="E9" t="n">
-        <v>86.31</v>
+        <v>92.2</v>
       </c>
       <c r="F9" t="n">
-        <v>74.50999999999999</v>
+        <v>77.63999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[4, 5, 5, 6, 9]</t>
+          <t>[3, 8, 0, 3, 5]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9562577839526032</v>
+        <v>0.9756836018829913</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9562577839526032</v>
+        <v>0.9756836018829913</v>
       </c>
       <c r="E10" t="n">
-        <v>82.15000000000001</v>
+        <v>99.66</v>
       </c>
       <c r="F10" t="n">
-        <v>66.42</v>
+        <v>69.11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[1, 2, 6, 0, 5]</t>
+          <t>[9, 3, 3, 0, 7]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9699355382564967</v>
+        <v>0.9717416091000314</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9699355382564967</v>
+        <v>0.9717416091000314</v>
       </c>
       <c r="E11" t="n">
-        <v>92.64</v>
+        <v>88.5</v>
       </c>
       <c r="F11" t="n">
-        <v>75.93000000000001</v>
+        <v>67.22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[3, 8, 8, 4, 8]</t>
+          <t>[2, 9, 0, 7, 1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -712,118 +712,118 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9563707471068276</v>
+        <v>0.9518719862229785</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9563707471068276</v>
+        <v>0.9518719862229785</v>
       </c>
       <c r="E12" t="n">
-        <v>77.84</v>
+        <v>89.33999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>56.81</v>
+        <v>64.52999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[0, 8, 5, 7, 5]</t>
+          <t>[3, 5, 7, 1, 3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9721139865579286</v>
+        <v>0.9752792501001937</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9721139865579286</v>
+        <v>0.9752792501001937</v>
       </c>
       <c r="E13" t="n">
-        <v>80.83000000000001</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>73.44999999999999</v>
+        <v>74.47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[8, 5, 0, 5, 8]</t>
+          <t>[2, 8, 8, 5, 2]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9761503839495406</v>
+        <v>0.9521226783788185</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9761503839495406</v>
+        <v>0.9521226783788185</v>
       </c>
       <c r="E14" t="n">
-        <v>96.49000000000001</v>
+        <v>82.72</v>
       </c>
       <c r="F14" t="n">
-        <v>73.92</v>
+        <v>74.30999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[5, 5, 3, 3, 8]</t>
+          <t>[5, 3, 2, 6, 2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 3]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9640636599772741</v>
+        <v>0.9789699108666158</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9640636599772741</v>
+        <v>0.9789699108666158</v>
       </c>
       <c r="E15" t="n">
-        <v>99.21000000000001</v>
+        <v>95.87</v>
       </c>
       <c r="F15" t="n">
-        <v>75.64</v>
+        <v>74.83999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[6, 5, 0, 1, 2]</t>
+          <t>[6, 5, 5, 5, 3]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9646923298577599</v>
+        <v>0.9736333353913512</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9646923298577599</v>
+        <v>0.9736333353913512</v>
       </c>
       <c r="E16" t="n">
-        <v>78.93000000000001</v>
+        <v>90.47</v>
       </c>
       <c r="F16" t="n">
-        <v>64.5</v>
+        <v>78.34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[8, 3, 3, 4, 3]</t>
+          <t>[2, 6, 5, 8, 9]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -832,46 +832,46 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9615482992488961</v>
+        <v>0.9489878701423996</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9615482992488961</v>
+        <v>0.9489878701423996</v>
       </c>
       <c r="E17" t="n">
-        <v>79.38</v>
+        <v>81.99999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>62.89000000000001</v>
+        <v>69.94</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[4, 5, 3, 8, 3]</t>
+          <t>[7, 0, 3, 2, 3]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9732147792775706</v>
+        <v>0.9645401928040594</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9732147792775706</v>
+        <v>0.9645401928040594</v>
       </c>
       <c r="E18" t="n">
-        <v>93.09</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>74.31999999999999</v>
+        <v>59.91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[5, 0, 7, 1, 8]</t>
+          <t>[1, 5, 4, 4, 6]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -880,118 +880,118 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9622104478632564</v>
+        <v>0.9615101566007945</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9622104478632564</v>
+        <v>0.9615101566007945</v>
       </c>
       <c r="E19" t="n">
-        <v>69.88</v>
+        <v>97.42</v>
       </c>
       <c r="F19" t="n">
-        <v>61.36</v>
+        <v>71.17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[3, 9, 6, 5, 7]</t>
+          <t>[0, 9, 3, 4, 3]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9747580769793297</v>
+        <v>0.9579141040389849</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9747580769793297</v>
+        <v>0.9579141040389849</v>
       </c>
       <c r="E20" t="n">
-        <v>88.88000000000001</v>
+        <v>86.52</v>
       </c>
       <c r="F20" t="n">
-        <v>78.51000000000001</v>
+        <v>57.21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[5, 5, 2, 8, 7]</t>
+          <t>[9, 1, 8, 2, 3]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9724036488206499</v>
+        <v>0.9503908823224977</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9724036488206499</v>
+        <v>0.9503908823224977</v>
       </c>
       <c r="E21" t="n">
-        <v>99.67</v>
+        <v>82.02</v>
       </c>
       <c r="F21" t="n">
-        <v>79.60000000000001</v>
+        <v>63.18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[5, 6, 2, 3, 8]</t>
+          <t>[6, 9, 3, 3, 9]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9642955499890962</v>
+        <v>0.9755101799023752</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9642955499890962</v>
+        <v>0.9755101799023752</v>
       </c>
       <c r="E22" t="n">
-        <v>92.50999999999999</v>
+        <v>99.67</v>
       </c>
       <c r="F22" t="n">
-        <v>71.09</v>
+        <v>75.69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[7, 1, 6, 9, 7]</t>
+          <t>[1, 4, 3, 5, 7]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9544991660199619</v>
+        <v>0.9764972436469818</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9544991660199619</v>
+        <v>0.9764972436469818</v>
       </c>
       <c r="E23" t="n">
-        <v>75.89</v>
+        <v>95.09</v>
       </c>
       <c r="F23" t="n">
-        <v>70.16</v>
+        <v>76.77999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[3, 8, 3, 6, 9]</t>
+          <t>[7, 6, 6, 1, 2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1000,22 +1000,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9570090056379446</v>
+        <v>0.9490547856023441</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9570090056379446</v>
+        <v>0.9490547856023441</v>
       </c>
       <c r="E24" t="n">
-        <v>77.55</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>61.25</v>
+        <v>69.92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[5, 5, 2, 3, 6]</t>
+          <t>[3, 6, 6, 2, 7]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1024,46 +1024,46 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9770779171539705</v>
+        <v>0.9741783538683657</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9770779171539705</v>
+        <v>0.9741783538683657</v>
       </c>
       <c r="E25" t="n">
-        <v>91.83</v>
+        <v>90.58000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>75.27000000000001</v>
+        <v>77.36999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[7, 5, 1, 9, 1]</t>
+          <t>[6, 8, 2, 3, 0]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9706359444474971</v>
+        <v>0.9766404270377187</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9706359444474971</v>
+        <v>0.9766404270377187</v>
       </c>
       <c r="E26" t="n">
-        <v>96.59</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>74.05</v>
+        <v>73.16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[1, 4, 4, 0, 0]</t>
+          <t>[0, 3, 1, 8, 5]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1072,166 +1072,166 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9693546485876188</v>
+        <v>0.9639599188029344</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9693546485876188</v>
+        <v>0.9639599188029344</v>
       </c>
       <c r="E27" t="n">
-        <v>83.95000000000002</v>
+        <v>84.25999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>70.99000000000001</v>
+        <v>60.89</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[0, 4, 1, 4, 8]</t>
+          <t>[4, 3, 3, 5, 3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9711139749195544</v>
+        <v>0.9788183046757324</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9711139749195544</v>
+        <v>0.9788183046757324</v>
       </c>
       <c r="E28" t="n">
-        <v>99.18000000000001</v>
+        <v>98.84</v>
       </c>
       <c r="F28" t="n">
-        <v>75.97</v>
+        <v>74.22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[5, 3, 8, 0, 5]</t>
+          <t>[9, 2, 3, 3, 5]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9735349341338189</v>
+        <v>0.9730278851134809</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9735349341338189</v>
+        <v>0.9730278851134809</v>
       </c>
       <c r="E29" t="n">
-        <v>83.98000000000002</v>
+        <v>88.43000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>70.66</v>
+        <v>68.31999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[1, 0, 2, 3, 5]</t>
+          <t>[3, 3, 3, 7, 2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9695999554428285</v>
+        <v>0.980673369113773</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9695999554428285</v>
+        <v>0.980673369113773</v>
       </c>
       <c r="E30" t="n">
-        <v>80.58000000000001</v>
+        <v>81.96000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>63.92</v>
+        <v>68.56999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[8, 9, 7, 6, 1]</t>
+          <t>[4, 2, 1, 7, 3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9699756418559842</v>
+        <v>0.9624212359320158</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9699756418559842</v>
+        <v>0.9624212359320158</v>
       </c>
       <c r="E31" t="n">
-        <v>97.85000000000001</v>
+        <v>86.44</v>
       </c>
       <c r="F31" t="n">
-        <v>77.57000000000001</v>
+        <v>67.76999999999998</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[1, 1, 0, 7, 3]</t>
+          <t>[7, 2, 8, 0, 9]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9702172427365852</v>
+        <v>0.95308536389596</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9702172427365852</v>
+        <v>0.95308536389596</v>
       </c>
       <c r="E32" t="n">
-        <v>88.22999999999999</v>
+        <v>84.33</v>
       </c>
       <c r="F32" t="n">
-        <v>76.12</v>
+        <v>69.19999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[3, 0, 8, 3, 4]</t>
+          <t>[2, 0, 1, 1, 3]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9765797535112294</v>
+        <v>0.9734690435238623</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9765797535112294</v>
+        <v>0.9734690435238623</v>
       </c>
       <c r="E33" t="n">
-        <v>92.25</v>
+        <v>93.25999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>76.59</v>
+        <v>56.63999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 3, 3]</t>
+          <t>[8, 0, 1, 6, 8]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1240,46 +1240,46 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.969678486663636</v>
+        <v>0.9577917434519251</v>
       </c>
       <c r="D34" t="n">
-        <v>0.969678486663636</v>
+        <v>0.9577917434519251</v>
       </c>
       <c r="E34" t="n">
-        <v>85.28999999999999</v>
+        <v>87.88999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>61.94</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[7, 8, 8, 6, 8]</t>
+          <t>[2, 7, 7, 6, 1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9752956729656572</v>
+        <v>0.9483159620696526</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9752956729656572</v>
+        <v>0.9483159620696526</v>
       </c>
       <c r="E35" t="n">
-        <v>95.32000000000001</v>
+        <v>80.08999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>79.40000000000001</v>
+        <v>72.75</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[6, 5, 7, 6, 3]</t>
+          <t>[8, 9, 1, 8, 5]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1288,46 +1288,46 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9539171446683603</v>
+        <v>0.9422170382268962</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9539171446683603</v>
+        <v>0.9422170382268962</v>
       </c>
       <c r="E36" t="n">
-        <v>67.65000000000001</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>65.85000000000001</v>
+        <v>69.41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[5, 8, 2, 5, 6]</t>
+          <t>[2, 2, 7, 3, 8]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9765032941618885</v>
+        <v>0.9627484944312852</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9765032941618885</v>
+        <v>0.9627484944312852</v>
       </c>
       <c r="E37" t="n">
-        <v>91.40000000000002</v>
+        <v>77.78999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>70.14</v>
+        <v>70.55</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[0, 3, 8, 3, 0]</t>
+          <t>[2, 6, 1, 3, 6]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1336,22 +1336,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9642525264564231</v>
+        <v>0.9631721168083184</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9642525264564231</v>
+        <v>0.9631721168083184</v>
       </c>
       <c r="E38" t="n">
-        <v>69.42999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="F38" t="n">
-        <v>61.5</v>
+        <v>62.69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[2, 4, 6, 7, 6]</t>
+          <t>[0, 5, 3, 6, 2]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1360,142 +1360,142 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9603798499328566</v>
+        <v>0.9606733380737708</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9603798499328566</v>
+        <v>0.9606733380737708</v>
       </c>
       <c r="E39" t="n">
-        <v>82.7</v>
+        <v>86.33000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>74.09</v>
+        <v>61.41999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[3, 2, 1, 2, 6]</t>
+          <t>[3, 5, 1, 6, 6]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9686165165707902</v>
+        <v>0.9798726863168989</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9686165165707902</v>
+        <v>0.9798726863168989</v>
       </c>
       <c r="E40" t="n">
-        <v>89.88000000000001</v>
+        <v>96.53</v>
       </c>
       <c r="F40" t="n">
-        <v>67.39000000000001</v>
+        <v>76.03999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[4, 6, 3, 5, 8]</t>
+          <t>[1, 5, 1, 9, 7]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9744266241392695</v>
+        <v>0.9801244471206905</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9744266241392695</v>
+        <v>0.9801244471206905</v>
       </c>
       <c r="E41" t="n">
-        <v>91.44</v>
+        <v>97.81</v>
       </c>
       <c r="F41" t="n">
-        <v>74.90000000000001</v>
+        <v>79.09</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[9, 9, 0, 0, 8]</t>
+          <t>[9, 3, 8, 7, 9]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.975965738437965</v>
+        <v>0.9446230429171506</v>
       </c>
       <c r="D42" t="n">
-        <v>0.975965738437965</v>
+        <v>0.9446230429171506</v>
       </c>
       <c r="E42" t="n">
-        <v>94.04000000000001</v>
+        <v>87.60999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>78.82000000000001</v>
+        <v>78.38</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[6, 0, 4, 1, 3]</t>
+          <t>[6, 0, 8, 0, 8]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9785893112396209</v>
+        <v>0.9553681441189978</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9785893112396209</v>
+        <v>0.9553681441189978</v>
       </c>
       <c r="E43" t="n">
-        <v>94.66999999999999</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>76.98999999999999</v>
+        <v>66.39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[1, 5, 3, 4, 3]</t>
+          <t>[5, 4, 1, 3, 8]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9647259421224429</v>
+        <v>0.9796302733143718</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9647259421224429</v>
+        <v>0.9796302733143718</v>
       </c>
       <c r="E44" t="n">
-        <v>80.69</v>
+        <v>97.44</v>
       </c>
       <c r="F44" t="n">
-        <v>63.37</v>
+        <v>76.19999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[0, 4, 2, 8, 1]</t>
+          <t>[4, 8, 0, 0, 5]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1504,22 +1504,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.964514047604531</v>
+        <v>0.964181999710321</v>
       </c>
       <c r="D45" t="n">
-        <v>0.964514047604531</v>
+        <v>0.964181999710321</v>
       </c>
       <c r="E45" t="n">
-        <v>86.97</v>
+        <v>97.23</v>
       </c>
       <c r="F45" t="n">
-        <v>65.86</v>
+        <v>66.33</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[9, 0, 9, 6, 5]</t>
+          <t>[3, 9, 5, 7, 9]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1528,70 +1528,70 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9498942026705512</v>
+        <v>0.9432070178094903</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9498942026705512</v>
+        <v>0.9432070178094903</v>
       </c>
       <c r="E46" t="n">
-        <v>81.13</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>66.47</v>
+        <v>63.99999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[6, 4, 3, 5, 1]</t>
+          <t>[1, 4, 9, 0, 6]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9773796472219918</v>
+        <v>0.9595372135534789</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9773796472219918</v>
+        <v>0.9595372135534789</v>
       </c>
       <c r="E47" t="n">
-        <v>93.86</v>
+        <v>97.74000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>76.33</v>
+        <v>63.59</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[9, 1, 8, 9, 6]</t>
+          <t>[9, 0, 6, 9, 1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9722054543577252</v>
+        <v>0.9432697995761935</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9722054543577252</v>
+        <v>0.9432697995761935</v>
       </c>
       <c r="E48" t="n">
-        <v>99.11999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="F48" t="n">
-        <v>70.78999999999999</v>
+        <v>59.58</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[8, 1, 0, 1, 6]</t>
+          <t>[8, 0, 2, 9, 5]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1600,64 +1600,64 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9664007748475051</v>
+        <v>0.9553614950827478</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9664007748475051</v>
+        <v>0.9553614950827478</v>
       </c>
       <c r="E49" t="n">
-        <v>73.03</v>
+        <v>87.35999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>57.54</v>
+        <v>66.31</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[4, 5, 2, 7, 1]</t>
+          <t>[8, 1, 1, 3, 5]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9608496435463989</v>
+        <v>0.9772252559194683</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9608496435463989</v>
+        <v>0.9772252559194683</v>
       </c>
       <c r="E50" t="n">
-        <v>86.53999999999999</v>
+        <v>94.14</v>
       </c>
       <c r="F50" t="n">
-        <v>70.37</v>
+        <v>71.53</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[0, 5, 3, 0, 3]</t>
+          <t>[5, 8, 8, 1, 6]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9821331141516636</v>
+        <v>0.9505027809474423</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9821331141516636</v>
+        <v>0.9505027809474423</v>
       </c>
       <c r="E51" t="n">
-        <v>81.96000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="F51" t="n">
-        <v>77.28999999999999</v>
+        <v>71.16999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_1.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_1.xlsx
@@ -463,55 +463,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[4, 5, 5, 3, 5]</t>
+          <t>[6, 2, 0, 0, 7]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9759671924549167</v>
+        <v>0.9641867690442503</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9759671924549167</v>
+        <v>0.9641867690442503</v>
       </c>
       <c r="E2" t="n">
-        <v>93.78999999999999</v>
+        <v>86.72</v>
       </c>
       <c r="F2" t="n">
-        <v>76.25</v>
+        <v>68.41</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[5, 7, 4, 9, 7]</t>
+          <t>[1, 1, 9, 8, 1]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9417537336538638</v>
+        <v>0.9708312268569051</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9417537336538638</v>
+        <v>0.9708312268569051</v>
       </c>
       <c r="E3" t="n">
-        <v>78.53</v>
+        <v>98.95</v>
       </c>
       <c r="F3" t="n">
-        <v>75.23999999999999</v>
+        <v>72.16000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[8, 6, 0, 2, 9]</t>
+          <t>[4, 4, 7, 2, 7]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,190 +520,190 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9577060555562528</v>
+        <v>0.9470583208658221</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9577060555562528</v>
+        <v>0.9470583208658221</v>
       </c>
       <c r="E4" t="n">
-        <v>89.08999999999999</v>
+        <v>89.02999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>66.37</v>
+        <v>74.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[0, 6, 7, 3, 3]</t>
+          <t>[1, 5, 9, 2, 1]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9749021815669767</v>
+        <v>0.9694437189089454</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9749021815669767</v>
+        <v>0.9694437189089454</v>
       </c>
       <c r="E5" t="n">
-        <v>88.92</v>
+        <v>96.94000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>76.21000000000001</v>
+        <v>79.99000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[9, 6, 7, 7, 8]</t>
+          <t>[1, 9, 1, 1, 8]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9312893881483579</v>
+        <v>0.9709505188189143</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9312893881483579</v>
+        <v>0.9709505188189143</v>
       </c>
       <c r="E6" t="n">
-        <v>71.94999999999999</v>
+        <v>98.95</v>
       </c>
       <c r="F6" t="n">
-        <v>75.3</v>
+        <v>72.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[3, 0, 3, 5, 8]</t>
+          <t>[8, 1, 3, 6, 7]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9810005391556259</v>
+        <v>0.9458392643251885</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9810005391556259</v>
+        <v>0.9458392643251885</v>
       </c>
       <c r="E7" t="n">
-        <v>99.66</v>
+        <v>82.7</v>
       </c>
       <c r="F7" t="n">
-        <v>69.11</v>
+        <v>71.92000000000002</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[2, 2, 3, 7, 0]</t>
+          <t>[1, 8, 8, 8, 4]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.977010846837901</v>
+        <v>0.9650792423038943</v>
       </c>
       <c r="D8" t="n">
-        <v>0.977010846837901</v>
+        <v>0.9650792423038943</v>
       </c>
       <c r="E8" t="n">
-        <v>98.2</v>
+        <v>87.75999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>74.09999999999999</v>
+        <v>66.69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[7, 3, 1, 7, 9]</t>
+          <t>[1, 3, 4, 3, 5]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9718673545344549</v>
+        <v>0.9536353824325708</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9718673545344549</v>
+        <v>0.9536353824325708</v>
       </c>
       <c r="E9" t="n">
-        <v>92.2</v>
+        <v>97.66</v>
       </c>
       <c r="F9" t="n">
-        <v>77.63999999999999</v>
+        <v>68.78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[3, 8, 0, 3, 5]</t>
+          <t>[0, 5, 5, 1, 9]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9756836018829913</v>
+        <v>0.9772333355965097</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9756836018829913</v>
+        <v>0.9772333355965097</v>
       </c>
       <c r="E10" t="n">
-        <v>99.66</v>
+        <v>95.69</v>
       </c>
       <c r="F10" t="n">
-        <v>69.11</v>
+        <v>73.78999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[9, 3, 3, 0, 7]</t>
+          <t>[3, 2, 6, 6, 5]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9717416091000314</v>
+        <v>0.9460595763368127</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9717416091000314</v>
+        <v>0.9460595763368127</v>
       </c>
       <c r="E11" t="n">
-        <v>88.5</v>
+        <v>78.75999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>67.22</v>
+        <v>76.27000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[2, 9, 0, 7, 1]</t>
+          <t>[1, 8, 0, 8, 5]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -712,118 +712,118 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9518719862229785</v>
+        <v>0.9473207730792947</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9518719862229785</v>
+        <v>0.9473207730792947</v>
       </c>
       <c r="E12" t="n">
-        <v>89.33999999999999</v>
+        <v>76.39</v>
       </c>
       <c r="F12" t="n">
-        <v>64.52999999999999</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[3, 5, 7, 1, 3]</t>
+          <t>[5, 8, 0, 8, 5]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9752792501001937</v>
+        <v>0.9734885442231538</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9752792501001937</v>
+        <v>0.9734885442231538</v>
       </c>
       <c r="E13" t="n">
-        <v>87.45999999999999</v>
+        <v>84.63000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>74.47</v>
+        <v>68.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[2, 8, 8, 5, 2]</t>
+          <t>[6, 5, 1, 8, 0]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9521226783788185</v>
+        <v>0.9717264851313694</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9521226783788185</v>
+        <v>0.9717264851313694</v>
       </c>
       <c r="E14" t="n">
-        <v>82.72</v>
+        <v>90.53999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>74.30999999999999</v>
+        <v>70.11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[5, 3, 2, 6, 2]</t>
+          <t>[9, 4, 9, 4, 3]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9789699108666158</v>
+        <v>0.9336592505176088</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9789699108666158</v>
+        <v>0.9336592505176088</v>
       </c>
       <c r="E15" t="n">
-        <v>95.87</v>
+        <v>99.63</v>
       </c>
       <c r="F15" t="n">
-        <v>74.83999999999999</v>
+        <v>68.01000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[6, 5, 5, 5, 3]</t>
+          <t>[3, 9, 6, 8, 4]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9736333353913512</v>
+        <v>0.9334063096505427</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9736333353913512</v>
+        <v>0.9334063096505427</v>
       </c>
       <c r="E16" t="n">
-        <v>90.47</v>
+        <v>87.63999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>78.34</v>
+        <v>68.05000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[2, 6, 5, 8, 9]</t>
+          <t>[8, 6, 4, 3, 0]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -832,22 +832,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9489878701423996</v>
+        <v>0.9435656038985286</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9489878701423996</v>
+        <v>0.9435656038985286</v>
       </c>
       <c r="E17" t="n">
-        <v>81.99999999999999</v>
+        <v>91.62</v>
       </c>
       <c r="F17" t="n">
-        <v>69.94</v>
+        <v>62.28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[7, 0, 3, 2, 3]</t>
+          <t>[3, 7, 6, 1, 1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -856,70 +856,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9645401928040594</v>
+        <v>0.9507972692074315</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9645401928040594</v>
+        <v>0.9507972692074315</v>
       </c>
       <c r="E18" t="n">
-        <v>78.98999999999999</v>
+        <v>87.82000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>59.91</v>
+        <v>72.27000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[1, 5, 4, 4, 6]</t>
+          <t>[9, 1, 8, 6, 8]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9615101566007945</v>
+        <v>0.9423447174190961</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9615101566007945</v>
+        <v>0.9423447174190961</v>
       </c>
       <c r="E19" t="n">
-        <v>97.42</v>
+        <v>85.47</v>
       </c>
       <c r="F19" t="n">
-        <v>71.17</v>
+        <v>74.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[0, 9, 3, 4, 3]</t>
+          <t>[0, 1, 9, 8, 6]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9579141040389849</v>
+        <v>0.9742165429343642</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9579141040389849</v>
+        <v>0.9742165429343642</v>
       </c>
       <c r="E20" t="n">
-        <v>86.52</v>
+        <v>99.42</v>
       </c>
       <c r="F20" t="n">
-        <v>57.21</v>
+        <v>72.70999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[9, 1, 8, 2, 3]</t>
+          <t>[5, 4, 0, 8, 8]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -928,70 +928,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9503908823224977</v>
+        <v>0.9487252185011981</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9503908823224977</v>
+        <v>0.9487252185011981</v>
       </c>
       <c r="E21" t="n">
-        <v>82.02</v>
+        <v>80.28999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>63.18</v>
+        <v>54.75999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[6, 9, 3, 3, 9]</t>
+          <t>[5, 1, 9, 2, 3]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9755101799023752</v>
+        <v>0.9452017902601898</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9755101799023752</v>
+        <v>0.9452017902601898</v>
       </c>
       <c r="E22" t="n">
-        <v>99.67</v>
+        <v>84.97</v>
       </c>
       <c r="F22" t="n">
-        <v>75.69</v>
+        <v>73.98</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[1, 4, 3, 5, 7]</t>
+          <t>[0, 6, 1, 9, 6]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9764972436469818</v>
+        <v>0.9787666140824129</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9764972436469818</v>
+        <v>0.9787666140824129</v>
       </c>
       <c r="E23" t="n">
-        <v>95.09</v>
+        <v>98.06000000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>76.77999999999999</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[7, 6, 6, 1, 2]</t>
+          <t>[9, 2, 9, 0, 6]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1000,166 +1000,166 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9490547856023441</v>
+        <v>0.9418625302302188</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9490547856023441</v>
+        <v>0.9418625302302188</v>
       </c>
       <c r="E24" t="n">
-        <v>84.84999999999999</v>
+        <v>83.78</v>
       </c>
       <c r="F24" t="n">
-        <v>69.92</v>
+        <v>71.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[3, 6, 6, 2, 7]</t>
+          <t>[6, 8, 4, 5, 3]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9741783538683657</v>
+        <v>0.9661926069855783</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9741783538683657</v>
+        <v>0.9661926069855783</v>
       </c>
       <c r="E25" t="n">
-        <v>90.58000000000001</v>
+        <v>97.24000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>77.36999999999999</v>
+        <v>78.51000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[6, 8, 2, 3, 0]</t>
+          <t>[9, 5, 4, 9, 5]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9766404270377187</v>
+        <v>0.9597786424956029</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9766404270377187</v>
+        <v>0.9597786424956029</v>
       </c>
       <c r="E26" t="n">
-        <v>98.29000000000001</v>
+        <v>95.61</v>
       </c>
       <c r="F26" t="n">
-        <v>73.16</v>
+        <v>78.59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[0, 3, 1, 8, 5]</t>
+          <t>[2, 0, 6, 5, 8]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9639599188029344</v>
+        <v>0.9584012899012045</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9639599188029344</v>
+        <v>0.9584012899012045</v>
       </c>
       <c r="E27" t="n">
-        <v>84.25999999999999</v>
+        <v>87.44</v>
       </c>
       <c r="F27" t="n">
-        <v>60.89</v>
+        <v>76.39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[4, 3, 3, 5, 3]</t>
+          <t>[2, 9, 4, 1, 6]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9788183046757324</v>
+        <v>0.9480265477201617</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9788183046757324</v>
+        <v>0.9480265477201617</v>
       </c>
       <c r="E28" t="n">
-        <v>98.84</v>
+        <v>84.24000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>74.22</v>
+        <v>69.17999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[9, 2, 3, 3, 5]</t>
+          <t>[8, 5, 9, 8, 1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9730278851134809</v>
+        <v>0.9283727097399195</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9730278851134809</v>
+        <v>0.9283727097399195</v>
       </c>
       <c r="E29" t="n">
-        <v>88.43000000000001</v>
+        <v>72.41</v>
       </c>
       <c r="F29" t="n">
-        <v>68.31999999999999</v>
+        <v>61.49999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 7, 2]</t>
+          <t>[1, 4, 7, 1, 3]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.980673369113773</v>
+        <v>0.9558989453334185</v>
       </c>
       <c r="D30" t="n">
-        <v>0.980673369113773</v>
+        <v>0.9558989453334185</v>
       </c>
       <c r="E30" t="n">
-        <v>81.96000000000001</v>
+        <v>94.96000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>68.56999999999999</v>
+        <v>68.42999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[4, 2, 1, 7, 3]</t>
+          <t>[8, 5, 1, 8, 0]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1168,22 +1168,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9624212359320158</v>
+        <v>0.9425697734325426</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9624212359320158</v>
+        <v>0.9425697734325426</v>
       </c>
       <c r="E31" t="n">
-        <v>86.44</v>
+        <v>76.38999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>67.76999999999998</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[7, 2, 8, 0, 9]</t>
+          <t>[4, 3, 9, 3, 6]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1192,70 +1192,70 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.95308536389596</v>
+        <v>0.9422499619611059</v>
       </c>
       <c r="D32" t="n">
-        <v>0.95308536389596</v>
+        <v>0.9422499619611059</v>
       </c>
       <c r="E32" t="n">
-        <v>84.33</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>69.19999999999999</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[2, 0, 1, 1, 3]</t>
+          <t>[5, 0, 0, 8, 2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9734690435238623</v>
+        <v>0.9635371027118959</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9734690435238623</v>
+        <v>0.9635371027118959</v>
       </c>
       <c r="E33" t="n">
-        <v>93.25999999999999</v>
+        <v>96.41</v>
       </c>
       <c r="F33" t="n">
-        <v>56.63999999999999</v>
+        <v>77.83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[8, 0, 1, 6, 8]</t>
+          <t>[5, 5, 9, 6, 0]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9577917434519251</v>
+        <v>0.9645849719071821</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9577917434519251</v>
+        <v>0.9645849719071821</v>
       </c>
       <c r="E34" t="n">
-        <v>87.88999999999999</v>
+        <v>96.21000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>67.59999999999999</v>
+        <v>78.91</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[2, 7, 7, 6, 1]</t>
+          <t>[7, 9, 9, 4, 4]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1264,22 +1264,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9483159620696526</v>
+        <v>0.9323180859842685</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9483159620696526</v>
+        <v>0.9323180859842685</v>
       </c>
       <c r="E35" t="n">
-        <v>80.08999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>72.75</v>
+        <v>68.86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[8, 9, 1, 8, 5]</t>
+          <t>[1, 3, 7, 6, 3]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1288,166 +1288,166 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9422170382268962</v>
+        <v>0.9500247493426935</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9422170382268962</v>
+        <v>0.9500247493426935</v>
       </c>
       <c r="E36" t="n">
-        <v>79.93000000000001</v>
+        <v>93.24000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>69.41</v>
+        <v>77.77000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[2, 2, 7, 3, 8]</t>
+          <t>[5, 9, 8, 6, 4]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9627484944312852</v>
+        <v>0.9582940942613637</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9627484944312852</v>
+        <v>0.9582940942613637</v>
       </c>
       <c r="E37" t="n">
-        <v>77.78999999999999</v>
+        <v>91.55000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>70.55</v>
+        <v>76.46000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[2, 6, 1, 3, 6]</t>
+          <t>[8, 5, 7, 8, 9]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9631721168083184</v>
+        <v>0.9586614832777164</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9631721168083184</v>
+        <v>0.9586614832777164</v>
       </c>
       <c r="E38" t="n">
-        <v>85.3</v>
+        <v>83.37</v>
       </c>
       <c r="F38" t="n">
-        <v>62.69</v>
+        <v>79.00999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[0, 5, 3, 6, 2]</t>
+          <t>[1, 9, 8, 5, 7]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9606733380737708</v>
+        <v>0.9601090838078831</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9606733380737708</v>
+        <v>0.9601090838078831</v>
       </c>
       <c r="E39" t="n">
-        <v>86.33000000000001</v>
+        <v>93.61</v>
       </c>
       <c r="F39" t="n">
-        <v>61.41999999999999</v>
+        <v>79.71000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[3, 5, 1, 6, 6]</t>
+          <t>[4, 7, 5, 1, 8]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9798726863168989</v>
+        <v>0.9485526091202499</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9798726863168989</v>
+        <v>0.9485526091202499</v>
       </c>
       <c r="E40" t="n">
-        <v>96.53</v>
+        <v>80.39</v>
       </c>
       <c r="F40" t="n">
-        <v>76.03999999999999</v>
+        <v>63.78</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[1, 5, 1, 9, 7]</t>
+          <t>[7, 7, 8, 4, 2]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9801244471206905</v>
+        <v>0.9384211432175618</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9801244471206905</v>
+        <v>0.9384211432175618</v>
       </c>
       <c r="E41" t="n">
-        <v>97.81</v>
+        <v>80.00999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>79.09</v>
+        <v>75.20999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[9, 3, 8, 7, 9]</t>
+          <t>[5, 0, 8, 1, 9]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9446230429171506</v>
+        <v>0.9785168032199179</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9446230429171506</v>
+        <v>0.9785168032199179</v>
       </c>
       <c r="E42" t="n">
-        <v>87.60999999999999</v>
+        <v>94.60000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>78.38</v>
+        <v>72.23999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[6, 0, 8, 0, 8]</t>
+          <t>[2, 1, 5, 9, 1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1456,46 +1456,46 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9553681441189978</v>
+        <v>0.9477858668850867</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9553681441189978</v>
+        <v>0.9477858668850867</v>
       </c>
       <c r="E43" t="n">
-        <v>90.65000000000001</v>
+        <v>79.55</v>
       </c>
       <c r="F43" t="n">
-        <v>66.39</v>
+        <v>68.48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[5, 4, 1, 3, 8]</t>
+          <t>[1, 8, 6, 5, 6]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9796302733143718</v>
+        <v>0.9704637025319029</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9796302733143718</v>
+        <v>0.9704637025319029</v>
       </c>
       <c r="E44" t="n">
-        <v>97.44</v>
+        <v>83.59</v>
       </c>
       <c r="F44" t="n">
-        <v>76.19999999999999</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[4, 8, 0, 0, 5]</t>
+          <t>[0, 0, 4, 8, 0]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1504,22 +1504,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.964181999710321</v>
+        <v>0.9626276306430902</v>
       </c>
       <c r="D45" t="n">
-        <v>0.964181999710321</v>
+        <v>0.9626276306430902</v>
       </c>
       <c r="E45" t="n">
-        <v>97.23</v>
+        <v>96.86000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>66.33</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[3, 9, 5, 7, 9]</t>
+          <t>[5, 9, 5, 7, 0]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1528,46 +1528,46 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9432070178094903</v>
+        <v>0.9376929088598656</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9432070178094903</v>
+        <v>0.9376929088598656</v>
       </c>
       <c r="E46" t="n">
-        <v>72.20999999999999</v>
+        <v>81.02000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>63.99999999999999</v>
+        <v>67.43000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[1, 4, 9, 0, 6]</t>
+          <t>[6, 8, 7, 4, 5]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9595372135534789</v>
+        <v>0.963906932102495</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9595372135534789</v>
+        <v>0.963906932102495</v>
       </c>
       <c r="E47" t="n">
-        <v>97.74000000000001</v>
+        <v>98.44</v>
       </c>
       <c r="F47" t="n">
-        <v>63.59</v>
+        <v>77.19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[9, 0, 6, 9, 1]</t>
+          <t>[7, 1, 9, 4, 7]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1576,22 +1576,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9432697995761935</v>
+        <v>0.9433130313850571</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9432697995761935</v>
+        <v>0.9433130313850571</v>
       </c>
       <c r="E48" t="n">
-        <v>90.97</v>
+        <v>87.95999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>59.58</v>
+        <v>72.72999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[8, 0, 2, 9, 5]</t>
+          <t>[0, 8, 9, 3, 0]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1600,46 +1600,46 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9553614950827478</v>
+        <v>0.9483397637481598</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9553614950827478</v>
+        <v>0.9483397637481598</v>
       </c>
       <c r="E49" t="n">
-        <v>87.35999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>66.31</v>
+        <v>61.51000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[8, 1, 1, 3, 5]</t>
+          <t>[8, 0, 1, 1, 8]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9772252559194683</v>
+        <v>0.9587535127619277</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9772252559194683</v>
+        <v>0.9587535127619277</v>
       </c>
       <c r="E50" t="n">
-        <v>94.14</v>
+        <v>80.42</v>
       </c>
       <c r="F50" t="n">
-        <v>71.53</v>
+        <v>54.53</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[5, 8, 8, 1, 6]</t>
+          <t>[0, 0, 6, 0, 8]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1648,16 +1648,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9505027809474423</v>
+        <v>0.9686921228767326</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9505027809474423</v>
+        <v>0.9686921228767326</v>
       </c>
       <c r="E51" t="n">
-        <v>80.8</v>
+        <v>89.72</v>
       </c>
       <c r="F51" t="n">
-        <v>71.16999999999999</v>
+        <v>53.11</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_1.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_1.xlsx
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[6, 2, 0, 0, 7]</t>
+          <t>[4, 3, 8, 8, 2]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,46 +472,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9641867690442503</v>
+        <v>0.9401699389509196</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9641867690442503</v>
+        <v>0.9401699389509196</v>
       </c>
       <c r="E2" t="n">
-        <v>86.72</v>
+        <v>79.08000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>68.41</v>
+        <v>74.64999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[1, 1, 9, 8, 1]</t>
+          <t>[9, 6, 1, 8, 0]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9708312268569051</v>
+        <v>0.9411121500295819</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9708312268569051</v>
+        <v>0.9411121500295819</v>
       </c>
       <c r="E3" t="n">
-        <v>98.95</v>
+        <v>95.81</v>
       </c>
       <c r="F3" t="n">
-        <v>72.16000000000001</v>
+        <v>65.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[4, 4, 7, 2, 7]</t>
+          <t>[3, 8, 3, 7, 6]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,118 +520,118 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9470583208658221</v>
+        <v>0.9371787136667467</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9470583208658221</v>
+        <v>0.9371787136667467</v>
       </c>
       <c r="E4" t="n">
-        <v>89.02999999999999</v>
+        <v>88.03</v>
       </c>
       <c r="F4" t="n">
-        <v>74.59</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[1, 5, 9, 2, 1]</t>
+          <t>[3, 9, 6, 9, 6]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9694437189089454</v>
+        <v>0.9304565844018187</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9694437189089454</v>
+        <v>0.9304565844018187</v>
       </c>
       <c r="E5" t="n">
-        <v>96.94000000000001</v>
+        <v>92.32999999999998</v>
       </c>
       <c r="F5" t="n">
-        <v>79.99000000000001</v>
+        <v>71.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[1, 9, 1, 1, 8]</t>
+          <t>[1, 5, 4, 0, 0]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9709505188189143</v>
+        <v>0.961723062836185</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9709505188189143</v>
+        <v>0.961723062836185</v>
       </c>
       <c r="E6" t="n">
-        <v>98.95</v>
+        <v>97.84</v>
       </c>
       <c r="F6" t="n">
-        <v>72.16</v>
+        <v>73.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[8, 1, 3, 6, 7]</t>
+          <t>[3, 1, 4, 7, 1]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9458392643251885</v>
+        <v>0.9580899681103136</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9458392643251885</v>
+        <v>0.9580899681103136</v>
       </c>
       <c r="E7" t="n">
-        <v>82.7</v>
+        <v>95.61999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>71.92000000000002</v>
+        <v>70.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[1, 8, 8, 8, 4]</t>
+          <t>[1, 1, 2, 5, 1]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9650792423038943</v>
+        <v>0.9813450349004684</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9650792423038943</v>
+        <v>0.9813450349004684</v>
       </c>
       <c r="E8" t="n">
-        <v>87.75999999999999</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>66.69</v>
+        <v>67.87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 3, 5]</t>
+          <t>[0, 8, 8, 3, 2]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,46 +640,46 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9536353824325708</v>
+        <v>0.9474678925701634</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9536353824325708</v>
+        <v>0.9474678925701634</v>
       </c>
       <c r="E9" t="n">
-        <v>97.66</v>
+        <v>89.66</v>
       </c>
       <c r="F9" t="n">
-        <v>68.78</v>
+        <v>75.03</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[0, 5, 5, 1, 9]</t>
+          <t>[1, 2, 1, 8, 6]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9772333355965097</v>
+        <v>0.9698770779744618</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9772333355965097</v>
+        <v>0.9698770779744618</v>
       </c>
       <c r="E10" t="n">
-        <v>95.69</v>
+        <v>98.05000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>73.78999999999999</v>
+        <v>68.22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[3, 2, 6, 6, 5]</t>
+          <t>[4, 8, 8, 9, 8]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -688,22 +688,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9460595763368127</v>
+        <v>0.9274218321826521</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9460595763368127</v>
+        <v>0.9274218321826521</v>
       </c>
       <c r="E11" t="n">
-        <v>78.75999999999999</v>
+        <v>87.91</v>
       </c>
       <c r="F11" t="n">
-        <v>76.27000000000001</v>
+        <v>69.69999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[1, 8, 0, 8, 5]</t>
+          <t>[2, 2, 8, 4, 4]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -712,70 +712,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9473207730792947</v>
+        <v>0.9506410138618057</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9473207730792947</v>
+        <v>0.9506410138618057</v>
       </c>
       <c r="E12" t="n">
-        <v>76.39</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>55.73</v>
+        <v>75.48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[5, 8, 0, 8, 5]</t>
+          <t>[4, 3, 4, 8, 6]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9734885442231538</v>
+        <v>0.9452901575666206</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9734885442231538</v>
+        <v>0.9452901575666206</v>
       </c>
       <c r="E13" t="n">
-        <v>84.63000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>68.09</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[6, 5, 1, 8, 0]</t>
+          <t>[4, 1, 1, 4, 6]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9717264851313694</v>
+        <v>0.9785029518904862</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9717264851313694</v>
+        <v>0.9785029518904862</v>
       </c>
       <c r="E14" t="n">
-        <v>90.53999999999999</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>70.11</v>
+        <v>71.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[9, 4, 9, 4, 3]</t>
+          <t>[1, 8, 9, 8, 9]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -784,22 +784,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9336592505176088</v>
+        <v>0.9351511071136691</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9336592505176088</v>
+        <v>0.9351511071136691</v>
       </c>
       <c r="E15" t="n">
-        <v>99.63</v>
+        <v>92.62</v>
       </c>
       <c r="F15" t="n">
-        <v>68.01000000000001</v>
+        <v>65.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[3, 9, 6, 8, 4]</t>
+          <t>[5, 7, 1, 1, 0]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -808,22 +808,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9334063096505427</v>
+        <v>0.956847188166411</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9334063096505427</v>
+        <v>0.956847188166411</v>
       </c>
       <c r="E16" t="n">
-        <v>87.63999999999999</v>
+        <v>98.28</v>
       </c>
       <c r="F16" t="n">
-        <v>68.05000000000001</v>
+        <v>59.46000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[8, 6, 4, 3, 0]</t>
+          <t>[8, 6, 7, 2, 2]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -832,22 +832,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9435656038985286</v>
+        <v>0.9353227701025146</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9435656038985286</v>
+        <v>0.9353227701025146</v>
       </c>
       <c r="E17" t="n">
-        <v>91.62</v>
+        <v>86.45</v>
       </c>
       <c r="F17" t="n">
-        <v>62.28</v>
+        <v>64.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[3, 7, 6, 1, 1]</t>
+          <t>[4, 2, 3, 4, 5]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -856,70 +856,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9507972692074315</v>
+        <v>0.954409159568736</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9507972692074315</v>
+        <v>0.954409159568736</v>
       </c>
       <c r="E18" t="n">
-        <v>87.82000000000001</v>
+        <v>78.02</v>
       </c>
       <c r="F18" t="n">
-        <v>72.27000000000001</v>
+        <v>79.99000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[9, 1, 8, 6, 8]</t>
+          <t>[4, 6, 1, 9, 3]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9423447174190961</v>
+        <v>0.9449758219573745</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9423447174190961</v>
+        <v>0.9449758219573745</v>
       </c>
       <c r="E19" t="n">
-        <v>85.47</v>
+        <v>82.11</v>
       </c>
       <c r="F19" t="n">
-        <v>74.33</v>
+        <v>70.04000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[0, 1, 9, 8, 6]</t>
+          <t>[0, 0, 2, 7, 3]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9742165429343642</v>
+        <v>0.9614280888553374</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9742165429343642</v>
+        <v>0.9614280888553374</v>
       </c>
       <c r="E20" t="n">
-        <v>99.42</v>
+        <v>97.07000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>72.70999999999999</v>
+        <v>74.96000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[5, 4, 0, 8, 8]</t>
+          <t>[1, 2, 3, 7, 7]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9487252185011981</v>
+        <v>0.9538031377330007</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9487252185011981</v>
+        <v>0.9538031377330007</v>
       </c>
       <c r="E21" t="n">
-        <v>80.28999999999999</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>54.75999999999999</v>
+        <v>61.02000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[5, 1, 9, 2, 3]</t>
+          <t>[3, 9, 8, 8, 4]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -952,46 +952,46 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9452017902601898</v>
+        <v>0.9302438816265728</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9452017902601898</v>
+        <v>0.9302438816265728</v>
       </c>
       <c r="E22" t="n">
-        <v>84.97</v>
+        <v>84.78999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>73.98</v>
+        <v>74.46000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[0, 6, 1, 9, 6]</t>
+          <t>[2, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9787666140824129</v>
+        <v>0.9810949379281155</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9787666140824129</v>
+        <v>0.9810949379281155</v>
       </c>
       <c r="E23" t="n">
-        <v>98.06000000000002</v>
+        <v>90.97</v>
       </c>
       <c r="F23" t="n">
-        <v>78.8</v>
+        <v>76.40000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[9, 2, 9, 0, 6]</t>
+          <t>[2, 2, 5, 9, 4]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1000,94 +1000,94 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9418625302302188</v>
+        <v>0.9460542211945818</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9418625302302188</v>
+        <v>0.9460542211945818</v>
       </c>
       <c r="E24" t="n">
-        <v>83.78</v>
+        <v>84.67000000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>71.28</v>
+        <v>77.00999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[6, 8, 4, 5, 3]</t>
+          <t>[6, 7, 4, 3, 3]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9661926069855783</v>
+        <v>0.9419069731142764</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9661926069855783</v>
+        <v>0.9419069731142764</v>
       </c>
       <c r="E25" t="n">
-        <v>97.24000000000001</v>
+        <v>82.39</v>
       </c>
       <c r="F25" t="n">
-        <v>78.51000000000001</v>
+        <v>72.47000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[9, 5, 4, 9, 5]</t>
+          <t>[1, 0, 1, 9, 7]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9597786424956029</v>
+        <v>0.9623592746273019</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9597786424956029</v>
+        <v>0.9623592746273019</v>
       </c>
       <c r="E26" t="n">
-        <v>95.61</v>
+        <v>95.5</v>
       </c>
       <c r="F26" t="n">
-        <v>78.59</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[2, 0, 6, 5, 8]</t>
+          <t>[0, 2, 3, 4, 8]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9584012899012045</v>
+        <v>0.96016104392935</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9584012899012045</v>
+        <v>0.96016104392935</v>
       </c>
       <c r="E27" t="n">
-        <v>87.44</v>
+        <v>84.01999999999998</v>
       </c>
       <c r="F27" t="n">
-        <v>76.39</v>
+        <v>78.10000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[2, 9, 4, 1, 6]</t>
+          <t>[4, 9, 4, 5, 4]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1096,22 +1096,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9480265477201617</v>
+        <v>0.9389786152954078</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9480265477201617</v>
+        <v>0.9389786152954078</v>
       </c>
       <c r="E28" t="n">
-        <v>84.24000000000001</v>
+        <v>81.21000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>69.17999999999999</v>
+        <v>78.11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[8, 5, 9, 8, 1]</t>
+          <t>[9, 3, 1, 8, 5]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1120,22 +1120,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9283727097399195</v>
+        <v>0.9451877247134257</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9283727097399195</v>
+        <v>0.9451877247134257</v>
       </c>
       <c r="E29" t="n">
-        <v>72.41</v>
+        <v>92.28</v>
       </c>
       <c r="F29" t="n">
-        <v>61.49999999999999</v>
+        <v>70.14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[1, 4, 7, 1, 3]</t>
+          <t>[6, 7, 0, 3, 7]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1144,46 +1144,46 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9558989453334185</v>
+        <v>0.9477256507539751</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9558989453334185</v>
+        <v>0.9477256507539751</v>
       </c>
       <c r="E30" t="n">
-        <v>94.96000000000001</v>
+        <v>98.56</v>
       </c>
       <c r="F30" t="n">
-        <v>68.42999999999999</v>
+        <v>64.57000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[8, 5, 1, 8, 0]</t>
+          <t>[7, 4, 1, 8, 2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9425697734325426</v>
+        <v>0.9653404130602919</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9425697734325426</v>
+        <v>0.9653404130602919</v>
       </c>
       <c r="E31" t="n">
-        <v>76.38999999999999</v>
+        <v>97.56</v>
       </c>
       <c r="F31" t="n">
-        <v>55.73</v>
+        <v>72.19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[4, 3, 9, 3, 6]</t>
+          <t>[0, 4, 2, 1, 2]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1192,70 +1192,70 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9422499619611059</v>
+        <v>0.9663867335307043</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9422499619611059</v>
+        <v>0.9663867335307043</v>
       </c>
       <c r="E32" t="n">
-        <v>98.18000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="F32" t="n">
-        <v>73.90000000000001</v>
+        <v>72.33999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[5, 0, 0, 8, 2]</t>
+          <t>[1, 1, 5, 5, 7]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9635371027118959</v>
+        <v>0.9559990863010366</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9635371027118959</v>
+        <v>0.9559990863010366</v>
       </c>
       <c r="E33" t="n">
-        <v>96.41</v>
+        <v>97.91999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>77.83</v>
+        <v>58.28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[5, 5, 9, 6, 0]</t>
+          <t>[3, 4, 1, 1, 6]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9645849719071821</v>
+        <v>0.9641009494564916</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9645849719071821</v>
+        <v>0.9641009494564916</v>
       </c>
       <c r="E34" t="n">
-        <v>96.21000000000001</v>
+        <v>77.58</v>
       </c>
       <c r="F34" t="n">
-        <v>78.91</v>
+        <v>64.19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[7, 9, 9, 4, 4]</t>
+          <t>[9, 7, 9, 1, 1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1264,22 +1264,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9323180859842685</v>
+        <v>0.9378838708650244</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9323180859842685</v>
+        <v>0.9378838708650244</v>
       </c>
       <c r="E35" t="n">
-        <v>92.90000000000001</v>
+        <v>92.36</v>
       </c>
       <c r="F35" t="n">
-        <v>68.86</v>
+        <v>58.40000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[1, 3, 7, 6, 3]</t>
+          <t>[0, 0, 1, 4, 0]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1288,118 +1288,118 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9500247493426935</v>
+        <v>0.9699432905758414</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9500247493426935</v>
+        <v>0.9699432905758414</v>
       </c>
       <c r="E36" t="n">
-        <v>93.24000000000001</v>
+        <v>98.19999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>77.77000000000001</v>
+        <v>74.19999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[5, 9, 8, 6, 4]</t>
+          <t>[7, 1, 8, 2, 1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9582940942613637</v>
+        <v>0.9458840500841665</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9582940942613637</v>
+        <v>0.9458840500841665</v>
       </c>
       <c r="E37" t="n">
-        <v>91.55000000000001</v>
+        <v>84.85000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>76.46000000000001</v>
+        <v>56.26000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[8, 5, 7, 8, 9]</t>
+          <t>[7, 9, 4, 5, 8]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9586614832777164</v>
+        <v>0.930362772771806</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9586614832777164</v>
+        <v>0.930362772771806</v>
       </c>
       <c r="E38" t="n">
-        <v>83.37</v>
+        <v>94.96000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>79.00999999999999</v>
+        <v>68.45</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[1, 9, 8, 5, 7]</t>
+          <t>[6, 6, 2, 5, 1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9601090838078831</v>
+        <v>0.9412325345825308</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9601090838078831</v>
+        <v>0.9412325345825308</v>
       </c>
       <c r="E39" t="n">
-        <v>93.61</v>
+        <v>89.78999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>79.71000000000001</v>
+        <v>63.77000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[4, 7, 5, 1, 8]</t>
+          <t>[6, 1, 4, 7, 6]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9485526091202499</v>
+        <v>0.9697601441675594</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9485526091202499</v>
+        <v>0.9697601441675594</v>
       </c>
       <c r="E40" t="n">
-        <v>80.39</v>
+        <v>98.66</v>
       </c>
       <c r="F40" t="n">
-        <v>63.78</v>
+        <v>74.46000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[7, 7, 8, 4, 2]</t>
+          <t>[5, 1, 6, 0, 8]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1408,22 +1408,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9384211432175618</v>
+        <v>0.9514453087553921</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9384211432175618</v>
+        <v>0.9514453087553921</v>
       </c>
       <c r="E41" t="n">
-        <v>80.00999999999999</v>
+        <v>98.59</v>
       </c>
       <c r="F41" t="n">
-        <v>75.20999999999999</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[5, 0, 8, 1, 9]</t>
+          <t>[2, 1, 1, 4, 8]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1432,22 +1432,22 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9785168032199179</v>
+        <v>0.9795931898129461</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9785168032199179</v>
+        <v>0.9795931898129461</v>
       </c>
       <c r="E42" t="n">
-        <v>94.60000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>72.23999999999999</v>
+        <v>78.23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[2, 1, 5, 9, 1]</t>
+          <t>[4, 1, 9, 1, 5]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1456,46 +1456,46 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9477858668850867</v>
+        <v>0.9548043384248172</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9477858668850867</v>
+        <v>0.9548043384248172</v>
       </c>
       <c r="E43" t="n">
-        <v>79.55</v>
+        <v>87.03</v>
       </c>
       <c r="F43" t="n">
-        <v>68.48</v>
+        <v>64.92999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[1, 8, 6, 5, 6]</t>
+          <t>[0, 8, 7, 7, 4]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9704637025319029</v>
+        <v>0.9377692795911273</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9704637025319029</v>
+        <v>0.9377692795911273</v>
       </c>
       <c r="E44" t="n">
-        <v>83.59</v>
+        <v>95.99000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>75.3</v>
+        <v>63.77999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[0, 0, 4, 8, 0]</t>
+          <t>[3, 7, 6, 3, 0]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1504,22 +1504,22 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9626276306430902</v>
+        <v>0.9438736355812848</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9626276306430902</v>
+        <v>0.9438736355812848</v>
       </c>
       <c r="E45" t="n">
-        <v>96.86000000000001</v>
+        <v>92.97</v>
       </c>
       <c r="F45" t="n">
-        <v>49.27</v>
+        <v>72.85000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[5, 9, 5, 7, 0]</t>
+          <t>[9, 6, 5, 1, 6]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1528,46 +1528,46 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9376929088598656</v>
+        <v>0.9401400264939177</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9376929088598656</v>
+        <v>0.9401400264939177</v>
       </c>
       <c r="E46" t="n">
-        <v>81.02000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="F46" t="n">
-        <v>67.43000000000001</v>
+        <v>63.58000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[6, 8, 7, 4, 5]</t>
+          <t>[6, 9, 0, 6, 6]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.963906932102495</v>
+        <v>0.9402733244931999</v>
       </c>
       <c r="D47" t="n">
-        <v>0.963906932102495</v>
+        <v>0.9402733244931999</v>
       </c>
       <c r="E47" t="n">
-        <v>98.44</v>
+        <v>98.63999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>77.19</v>
+        <v>67.38</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[7, 1, 9, 4, 7]</t>
+          <t>[2, 6, 8, 9, 1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1576,22 +1576,22 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9433130313850571</v>
+        <v>0.9364502733889466</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9433130313850571</v>
+        <v>0.9364502733889466</v>
       </c>
       <c r="E48" t="n">
-        <v>87.95999999999999</v>
+        <v>86.96000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>72.72999999999999</v>
+        <v>64.73</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[0, 8, 9, 3, 0]</t>
+          <t>[6, 2, 0, 4, 8]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9483397637481598</v>
+        <v>0.9556383696195295</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9483397637481598</v>
+        <v>0.9556383696195295</v>
       </c>
       <c r="E49" t="n">
-        <v>94.40000000000001</v>
+        <v>87.19</v>
       </c>
       <c r="F49" t="n">
-        <v>61.51000000000001</v>
+        <v>72.44</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[8, 0, 1, 1, 8]</t>
+          <t>[1, 5, 2, 4, 0]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9587535127619277</v>
+        <v>0.9564112586220112</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9587535127619277</v>
+        <v>0.9564112586220112</v>
       </c>
       <c r="E50" t="n">
-        <v>80.42</v>
+        <v>88.98999999999998</v>
       </c>
       <c r="F50" t="n">
-        <v>54.53</v>
+        <v>72.09</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[0, 0, 6, 0, 8]</t>
+          <t>[4, 0, 7, 5, 6]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1648,16 +1648,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9686921228767326</v>
+        <v>0.9472327345294924</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9686921228767326</v>
+        <v>0.9472327345294924</v>
       </c>
       <c r="E51" t="n">
-        <v>89.72</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>53.11</v>
+        <v>68.67</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_1.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_1.xlsx
@@ -463,127 +463,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[4, 3, 8, 8, 2]</t>
+          <t>[3, 4, 4, 9, 7]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9401699389509196</v>
+        <v>0.9709179709934334</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9401699389509196</v>
+        <v>0.9709179709934334</v>
       </c>
       <c r="E2" t="n">
-        <v>79.08000000000001</v>
+        <v>99.55</v>
       </c>
       <c r="F2" t="n">
-        <v>74.64999999999999</v>
+        <v>77.66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[9, 6, 1, 8, 0]</t>
+          <t>[8, 1, 7, 9, 0]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9411121500295819</v>
+        <v>0.9643468182838474</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9411121500295819</v>
+        <v>0.9643468182838474</v>
       </c>
       <c r="E3" t="n">
-        <v>95.81</v>
+        <v>105.77</v>
       </c>
       <c r="F3" t="n">
-        <v>65.66</v>
+        <v>88.11000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[3, 8, 3, 7, 6]</t>
+          <t>[1, 4, 3, 4, 5]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9371787136667467</v>
+        <v>0.9753082887750733</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9371787136667467</v>
+        <v>0.9753082887750733</v>
       </c>
       <c r="E4" t="n">
-        <v>88.03</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>69.40000000000001</v>
+        <v>80.68000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[3, 9, 6, 9, 6]</t>
+          <t>[0, 5, 8, 4, 8]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9304565844018187</v>
+        <v>0.9700401250492376</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9304565844018187</v>
+        <v>0.9700401250492376</v>
       </c>
       <c r="E5" t="n">
-        <v>92.32999999999998</v>
+        <v>111.77</v>
       </c>
       <c r="F5" t="n">
-        <v>71.92</v>
+        <v>84.96000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[1, 5, 4, 0, 0]</t>
+          <t>[1, 4, 2, 3, 6]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 3, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.961723062836185</v>
+        <v>0.9791655212963492</v>
       </c>
       <c r="D6" t="n">
-        <v>0.961723062836185</v>
+        <v>0.9791655212963492</v>
       </c>
       <c r="E6" t="n">
-        <v>97.84</v>
+        <v>120</v>
       </c>
       <c r="F6" t="n">
-        <v>73.02</v>
+        <v>96.71000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[3, 1, 4, 7, 1]</t>
+          <t>[8, 8, 5, 9, 3]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -592,334 +592,334 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9580899681103136</v>
+        <v>0.9395034058233364</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9580899681103136</v>
+        <v>0.9395034058233364</v>
       </c>
       <c r="E7" t="n">
-        <v>95.61999999999999</v>
+        <v>104.43</v>
       </c>
       <c r="F7" t="n">
-        <v>70.91</v>
+        <v>81.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 5, 1]</t>
+          <t>[1, 0, 4, 7, 3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9813450349004684</v>
+        <v>0.9765678609365428</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9813450349004684</v>
+        <v>0.9765678609365428</v>
       </c>
       <c r="E8" t="n">
-        <v>99.84999999999999</v>
+        <v>114.46</v>
       </c>
       <c r="F8" t="n">
-        <v>67.87</v>
+        <v>94.67999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[0, 8, 8, 3, 2]</t>
+          <t>[4, 6, 6, 4, 7]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9474678925701634</v>
+        <v>0.9731103863613442</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9474678925701634</v>
+        <v>0.9731103863613442</v>
       </c>
       <c r="E9" t="n">
-        <v>89.66</v>
+        <v>113.7</v>
       </c>
       <c r="F9" t="n">
-        <v>75.03</v>
+        <v>91.98999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 8, 6]</t>
+          <t>[1, 8, 4, 3, 6]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9698770779744618</v>
+        <v>0.9738859519171408</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9698770779744618</v>
+        <v>0.9738859519171408</v>
       </c>
       <c r="E10" t="n">
-        <v>98.05000000000001</v>
+        <v>101.45</v>
       </c>
       <c r="F10" t="n">
-        <v>68.22</v>
+        <v>79.21000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[4, 8, 8, 9, 8]</t>
+          <t>[4, 5, 1, 2, 7]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9274218321826521</v>
+        <v>0.9594142871298563</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9274218321826521</v>
+        <v>0.9594142871298563</v>
       </c>
       <c r="E11" t="n">
-        <v>87.91</v>
+        <v>102.26</v>
       </c>
       <c r="F11" t="n">
-        <v>69.69999999999999</v>
+        <v>94.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[2, 2, 8, 4, 4]</t>
+          <t>[5, 2, 8, 3, 7]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9506410138618057</v>
+        <v>0.9523306430054703</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9506410138618057</v>
+        <v>0.9523306430054703</v>
       </c>
       <c r="E12" t="n">
-        <v>72.65000000000001</v>
+        <v>106.04</v>
       </c>
       <c r="F12" t="n">
-        <v>75.48</v>
+        <v>91.49000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[4, 3, 4, 8, 6]</t>
+          <t>[7, 1, 2, 4, 5]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 2]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9452901575666206</v>
+        <v>0.9737958141154368</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9452901575666206</v>
+        <v>0.9737958141154368</v>
       </c>
       <c r="E13" t="n">
-        <v>77.40000000000001</v>
+        <v>107.23</v>
       </c>
       <c r="F13" t="n">
-        <v>74.3</v>
+        <v>99.03</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[4, 1, 1, 4, 6]</t>
+          <t>[0, 0, 1, 9, 3]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9785029518904862</v>
+        <v>0.9717160518164516</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9785029518904862</v>
+        <v>0.9717160518164516</v>
       </c>
       <c r="E14" t="n">
-        <v>90.68000000000001</v>
+        <v>110.99</v>
       </c>
       <c r="F14" t="n">
-        <v>71.84</v>
+        <v>90.24000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[1, 8, 9, 8, 9]</t>
+          <t>[5, 4, 6, 1, 6]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9351511071136691</v>
+        <v>0.9923932205645092</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9351511071136691</v>
+        <v>0.9923932205645092</v>
       </c>
       <c r="E15" t="n">
-        <v>92.62</v>
+        <v>107.92</v>
       </c>
       <c r="F15" t="n">
-        <v>65.44</v>
+        <v>97.78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[5, 7, 1, 1, 0]</t>
+          <t>[6, 6, 4, 7, 1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.956847188166411</v>
+        <v>0.9722693636806805</v>
       </c>
       <c r="D16" t="n">
-        <v>0.956847188166411</v>
+        <v>0.9722693636806805</v>
       </c>
       <c r="E16" t="n">
-        <v>98.28</v>
+        <v>110.16</v>
       </c>
       <c r="F16" t="n">
-        <v>59.46000000000001</v>
+        <v>96.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[8, 6, 7, 2, 2]</t>
+          <t>[2, 9, 1, 7, 3]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9353227701025146</v>
+        <v>0.9733494018449049</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9353227701025146</v>
+        <v>0.9733494018449049</v>
       </c>
       <c r="E17" t="n">
-        <v>86.45</v>
+        <v>101.72</v>
       </c>
       <c r="F17" t="n">
-        <v>64.92</v>
+        <v>86.30000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[4, 2, 3, 4, 5]</t>
+          <t>[2, 6, 0, 3, 1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.954409159568736</v>
+        <v>0.9764428128616288</v>
       </c>
       <c r="D18" t="n">
-        <v>0.954409159568736</v>
+        <v>0.9764428128616288</v>
       </c>
       <c r="E18" t="n">
-        <v>78.02</v>
+        <v>107.06</v>
       </c>
       <c r="F18" t="n">
-        <v>79.99000000000001</v>
+        <v>87.27000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[4, 6, 1, 9, 3]</t>
+          <t>[4, 7, 4, 7, 6]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9449758219573745</v>
+        <v>0.9923452239051341</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9449758219573745</v>
+        <v>0.9923452239051341</v>
       </c>
       <c r="E19" t="n">
-        <v>82.11</v>
+        <v>118.5</v>
       </c>
       <c r="F19" t="n">
-        <v>70.04000000000001</v>
+        <v>98.76000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[0, 0, 2, 7, 3]</t>
+          <t>[1, 2, 1, 1, 9]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9614280888553374</v>
+        <v>0.9772492032617025</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9614280888553374</v>
+        <v>0.9772492032617025</v>
       </c>
       <c r="E20" t="n">
-        <v>97.07000000000001</v>
+        <v>100.33</v>
       </c>
       <c r="F20" t="n">
-        <v>74.96000000000001</v>
+        <v>94.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[1, 2, 3, 7, 7]</t>
+          <t>[7, 2, 4, 0, 0]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -928,166 +928,166 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9538031377330007</v>
+        <v>0.9548986699772187</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9538031377330007</v>
+        <v>0.9548986699772187</v>
       </c>
       <c r="E21" t="n">
-        <v>86.93000000000001</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>61.02000000000001</v>
+        <v>73.86</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[3, 9, 8, 8, 4]</t>
+          <t>[3, 9, 7, 6, 0]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9302438816265728</v>
+        <v>0.9882073186698486</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9302438816265728</v>
+        <v>0.9882073186698486</v>
       </c>
       <c r="E22" t="n">
-        <v>84.78999999999999</v>
+        <v>118.84</v>
       </c>
       <c r="F22" t="n">
-        <v>74.46000000000001</v>
+        <v>93.31999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 3, 1]</t>
+          <t>[7, 8, 7, 6, 3]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 2]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9810949379281155</v>
+        <v>0.9708538233749379</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9810949379281155</v>
+        <v>0.9708538233749379</v>
       </c>
       <c r="E23" t="n">
-        <v>90.97</v>
+        <v>118.25</v>
       </c>
       <c r="F23" t="n">
-        <v>76.40000000000001</v>
+        <v>96.64</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[2, 2, 5, 9, 4]</t>
+          <t>[0, 1, 7, 7, 1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 2]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9460542211945818</v>
+        <v>0.975188238871066</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9460542211945818</v>
+        <v>0.975188238871066</v>
       </c>
       <c r="E24" t="n">
-        <v>84.67000000000002</v>
+        <v>105.76</v>
       </c>
       <c r="F24" t="n">
-        <v>77.00999999999999</v>
+        <v>97.03</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[6, 7, 4, 3, 3]</t>
+          <t>[8, 5, 5, 8, 4]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9419069731142764</v>
+        <v>0.9674950177337446</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9419069731142764</v>
+        <v>0.9674950177337446</v>
       </c>
       <c r="E25" t="n">
-        <v>82.39</v>
+        <v>108.28</v>
       </c>
       <c r="F25" t="n">
-        <v>72.47000000000001</v>
+        <v>99.20999999999998</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[1, 0, 1, 9, 7]</t>
+          <t>[7, 8, 6, 4, 3]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9623592746273019</v>
+        <v>0.9900671421578395</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9623592746273019</v>
+        <v>0.9900671421578395</v>
       </c>
       <c r="E26" t="n">
-        <v>95.5</v>
+        <v>116.19</v>
       </c>
       <c r="F26" t="n">
-        <v>59.52</v>
+        <v>89.29000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[0, 2, 3, 4, 8]</t>
+          <t>[0, 5, 9, 5, 4]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.96016104392935</v>
+        <v>0.9681880126334756</v>
       </c>
       <c r="D27" t="n">
-        <v>0.96016104392935</v>
+        <v>0.9681880126334756</v>
       </c>
       <c r="E27" t="n">
-        <v>84.01999999999998</v>
+        <v>106.84</v>
       </c>
       <c r="F27" t="n">
-        <v>78.10000000000001</v>
+        <v>89.88</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[4, 9, 4, 5, 4]</t>
+          <t>[7, 1, 6, 9, 5]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1096,166 +1096,166 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9389786152954078</v>
+        <v>0.9449843134623654</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9389786152954078</v>
+        <v>0.9449843134623654</v>
       </c>
       <c r="E28" t="n">
-        <v>81.21000000000001</v>
+        <v>75.67</v>
       </c>
       <c r="F28" t="n">
-        <v>78.11</v>
+        <v>70.49000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[9, 3, 1, 8, 5]</t>
+          <t>[4, 6, 5, 6, 9]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9451877247134257</v>
+        <v>0.9749529198937793</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9451877247134257</v>
+        <v>0.9749529198937793</v>
       </c>
       <c r="E29" t="n">
-        <v>92.28</v>
+        <v>115.29</v>
       </c>
       <c r="F29" t="n">
-        <v>70.14</v>
+        <v>97.38000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[6, 7, 0, 3, 7]</t>
+          <t>[9, 8, 5, 5, 5]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9477256507539751</v>
+        <v>0.961534424302402</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9477256507539751</v>
+        <v>0.961534424302402</v>
       </c>
       <c r="E30" t="n">
-        <v>98.56</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>64.57000000000001</v>
+        <v>87.09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[7, 4, 1, 8, 2]</t>
+          <t>[5, 1, 0, 8, 5]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9653404130602919</v>
+        <v>0.9718396897403527</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9653404130602919</v>
+        <v>0.9718396897403527</v>
       </c>
       <c r="E31" t="n">
-        <v>97.56</v>
+        <v>95.78</v>
       </c>
       <c r="F31" t="n">
-        <v>72.19</v>
+        <v>89.21000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[0, 4, 2, 1, 2]</t>
+          <t>[3, 3, 9, 4, 4]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9663867335307043</v>
+        <v>0.9745671731700105</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9663867335307043</v>
+        <v>0.9745671731700105</v>
       </c>
       <c r="E32" t="n">
-        <v>80.5</v>
+        <v>118.43</v>
       </c>
       <c r="F32" t="n">
-        <v>72.33999999999999</v>
+        <v>89.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[1, 1, 5, 5, 7]</t>
+          <t>[7, 0, 7, 9, 5]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9559990863010366</v>
+        <v>0.969188258125645</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9559990863010366</v>
+        <v>0.969188258125645</v>
       </c>
       <c r="E33" t="n">
-        <v>97.91999999999999</v>
+        <v>91.41</v>
       </c>
       <c r="F33" t="n">
-        <v>58.28</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[3, 4, 1, 1, 6]</t>
+          <t>[8, 1, 9, 3, 4]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9641009494564916</v>
+        <v>0.9641273305420084</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9641009494564916</v>
+        <v>0.9641273305420084</v>
       </c>
       <c r="E34" t="n">
-        <v>77.58</v>
+        <v>119.64</v>
       </c>
       <c r="F34" t="n">
-        <v>64.19</v>
+        <v>92.58000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[9, 7, 9, 1, 1]</t>
+          <t>[8, 7, 6, 4, 4]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1264,400 +1264,400 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9378838708650244</v>
+        <v>0.9431100646598884</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9378838708650244</v>
+        <v>0.9431100646598884</v>
       </c>
       <c r="E35" t="n">
-        <v>92.36</v>
+        <v>84.77000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>58.40000000000001</v>
+        <v>65.29000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[0, 0, 1, 4, 0]</t>
+          <t>[9, 9, 3, 5, 7]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9699432905758414</v>
+        <v>0.9634507074072963</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9699432905758414</v>
+        <v>0.9634507074072963</v>
       </c>
       <c r="E36" t="n">
-        <v>98.19999999999999</v>
+        <v>97.75999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>74.19999999999999</v>
+        <v>83.84999999999998</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[7, 1, 8, 2, 1]</t>
+          <t>[4, 2, 3, 4, 2]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9458840500841665</v>
+        <v>0.9738322841271023</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9458840500841665</v>
+        <v>0.9738322841271023</v>
       </c>
       <c r="E37" t="n">
-        <v>84.85000000000001</v>
+        <v>108.27</v>
       </c>
       <c r="F37" t="n">
-        <v>56.26000000000001</v>
+        <v>84.59999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[7, 9, 4, 5, 8]</t>
+          <t>[7, 6, 0, 6, 9]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.930362772771806</v>
+        <v>0.9717881748570362</v>
       </c>
       <c r="D38" t="n">
-        <v>0.930362772771806</v>
+        <v>0.9717881748570362</v>
       </c>
       <c r="E38" t="n">
-        <v>94.96000000000001</v>
+        <v>104.18</v>
       </c>
       <c r="F38" t="n">
-        <v>68.45</v>
+        <v>83.89</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[6, 6, 2, 5, 1]</t>
+          <t>[6, 5, 7, 1, 3]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9412325345825308</v>
+        <v>0.9922579710506689</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9412325345825308</v>
+        <v>0.9922579710506689</v>
       </c>
       <c r="E39" t="n">
-        <v>89.78999999999999</v>
+        <v>99.78</v>
       </c>
       <c r="F39" t="n">
-        <v>63.77000000000001</v>
+        <v>93.50000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[6, 1, 4, 7, 6]</t>
+          <t>[7, 9, 8, 5, 6]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[2, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9697601441675594</v>
+        <v>0.9652211156001111</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9697601441675594</v>
+        <v>0.9652211156001111</v>
       </c>
       <c r="E40" t="n">
-        <v>98.66</v>
+        <v>110.26</v>
       </c>
       <c r="F40" t="n">
-        <v>74.46000000000001</v>
+        <v>94.18000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[5, 1, 6, 0, 8]</t>
+          <t>[0, 8, 8, 3, 1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9514453087553921</v>
+        <v>0.9684344050066056</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9514453087553921</v>
+        <v>0.9684344050066056</v>
       </c>
       <c r="E41" t="n">
-        <v>98.59</v>
+        <v>116.34</v>
       </c>
       <c r="F41" t="n">
-        <v>65.59999999999999</v>
+        <v>85.36000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 4, 8]</t>
+          <t>[1, 8, 5, 8, 5]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9795931898129461</v>
+        <v>0.9624775234118754</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9795931898129461</v>
+        <v>0.9624775234118754</v>
       </c>
       <c r="E42" t="n">
-        <v>91.18000000000001</v>
+        <v>93.81</v>
       </c>
       <c r="F42" t="n">
-        <v>78.23</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[4, 1, 9, 1, 5]</t>
+          <t>[3, 3, 4, 2, 5]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9548043384248172</v>
+        <v>0.9729693876042382</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9548043384248172</v>
+        <v>0.9729693876042382</v>
       </c>
       <c r="E43" t="n">
-        <v>87.03</v>
+        <v>101.25</v>
       </c>
       <c r="F43" t="n">
-        <v>64.92999999999999</v>
+        <v>84.47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[0, 8, 7, 7, 4]</t>
+          <t>[6, 1, 7, 4, 8]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9377692795911273</v>
+        <v>0.970172149940454</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9377692795911273</v>
+        <v>0.970172149940454</v>
       </c>
       <c r="E44" t="n">
-        <v>95.99000000000001</v>
+        <v>117.49</v>
       </c>
       <c r="F44" t="n">
-        <v>63.77999999999999</v>
+        <v>93.81999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[3, 7, 6, 3, 0]</t>
+          <t>[2, 3, 0, 7, 0]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9438736355812848</v>
+        <v>0.9716030760851949</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9438736355812848</v>
+        <v>0.9716030760851949</v>
       </c>
       <c r="E45" t="n">
-        <v>92.97</v>
+        <v>113.95</v>
       </c>
       <c r="F45" t="n">
-        <v>72.85000000000001</v>
+        <v>89.24000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[9, 6, 5, 1, 6]</t>
+          <t>[1, 3, 0, 7, 6]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9401400264939177</v>
+        <v>0.9714724063508187</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9401400264939177</v>
+        <v>0.9714724063508187</v>
       </c>
       <c r="E46" t="n">
-        <v>95.5</v>
+        <v>97.97</v>
       </c>
       <c r="F46" t="n">
-        <v>63.58000000000001</v>
+        <v>83.69</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[6, 9, 0, 6, 6]</t>
+          <t>[4, 4, 9, 8, 6]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9402733244931999</v>
+        <v>0.9653486111853019</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9402733244931999</v>
+        <v>0.9653486111853019</v>
       </c>
       <c r="E47" t="n">
-        <v>98.63999999999999</v>
+        <v>110.71</v>
       </c>
       <c r="F47" t="n">
-        <v>67.38</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[2, 6, 8, 9, 1]</t>
+          <t>[4, 4, 1, 5, 0]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9364502733889466</v>
+        <v>0.9800672474015355</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9364502733889466</v>
+        <v>0.9800672474015355</v>
       </c>
       <c r="E48" t="n">
-        <v>86.96000000000001</v>
+        <v>115.02</v>
       </c>
       <c r="F48" t="n">
-        <v>64.73</v>
+        <v>99.84999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[6, 2, 0, 4, 8]</t>
+          <t>[7, 1, 4, 0, 1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9556383696195295</v>
+        <v>0.9811365408300138</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9556383696195295</v>
+        <v>0.9811365408300138</v>
       </c>
       <c r="E49" t="n">
-        <v>87.19</v>
+        <v>118.12</v>
       </c>
       <c r="F49" t="n">
-        <v>72.44</v>
+        <v>97.80000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[1, 5, 2, 4, 0]</t>
+          <t>[8, 1, 6, 3, 6]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9564112586220112</v>
+        <v>0.992011662280495</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9564112586220112</v>
+        <v>0.992011662280495</v>
       </c>
       <c r="E50" t="n">
-        <v>88.98999999999998</v>
+        <v>117.19</v>
       </c>
       <c r="F50" t="n">
-        <v>72.09</v>
+        <v>93.32000000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[4, 0, 7, 5, 6]</t>
+          <t>[6, 3, 5, 0, 3]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9472327345294924</v>
+        <v>0.9571074918667767</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9472327345294924</v>
+        <v>0.9571074918667767</v>
       </c>
       <c r="E51" t="n">
-        <v>98.15000000000001</v>
+        <v>114.23</v>
       </c>
       <c r="F51" t="n">
-        <v>68.67</v>
+        <v>90.31</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_1.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_1.xlsx
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[3, 4, 4, 9, 7]</t>
+          <t>[2, 0, 2, 7, 9]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,790 +472,790 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9709179709934334</v>
+        <v>0.975246605656324</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9709179709934334</v>
+        <v>0.975246605656324</v>
       </c>
       <c r="E2" t="n">
-        <v>99.55</v>
+        <v>118.56</v>
       </c>
       <c r="F2" t="n">
-        <v>77.66</v>
+        <v>83.83000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[8, 1, 7, 9, 0]</t>
+          <t>[2, 5, 8, 7, 6]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9643468182838474</v>
+        <v>0.9459390931035327</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9643468182838474</v>
+        <v>0.9459390931035327</v>
       </c>
       <c r="E3" t="n">
-        <v>105.77</v>
+        <v>106.23</v>
       </c>
       <c r="F3" t="n">
-        <v>88.11000000000001</v>
+        <v>72.72999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[1, 4, 3, 4, 5]</t>
+          <t>[2, 8, 8, 4, 4]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9753082887750733</v>
+        <v>0.9643686873671465</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9753082887750733</v>
+        <v>0.9643686873671465</v>
       </c>
       <c r="E4" t="n">
-        <v>95.54000000000001</v>
+        <v>113.97</v>
       </c>
       <c r="F4" t="n">
-        <v>80.68000000000001</v>
+        <v>77.62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[0, 5, 8, 4, 8]</t>
+          <t>[5, 5, 3, 7, 1]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9700401250492376</v>
+        <v>0.9633913596323569</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9700401250492376</v>
+        <v>0.9633913596323569</v>
       </c>
       <c r="E5" t="n">
-        <v>111.77</v>
+        <v>106.01</v>
       </c>
       <c r="F5" t="n">
-        <v>84.96000000000001</v>
+        <v>74.17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[1, 4, 2, 3, 6]</t>
+          <t>[9, 2, 5, 1, 1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 3, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9791655212963492</v>
+        <v>0.9631708237387082</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9791655212963492</v>
+        <v>0.9631708237387082</v>
       </c>
       <c r="E6" t="n">
-        <v>120</v>
+        <v>110.17</v>
       </c>
       <c r="F6" t="n">
-        <v>96.71000000000001</v>
+        <v>81.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[8, 8, 5, 9, 3]</t>
+          <t>[6, 3, 8, 8, 1]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9395034058233364</v>
+        <v>0.9381231808711074</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9395034058233364</v>
+        <v>0.9381231808711074</v>
       </c>
       <c r="E7" t="n">
-        <v>104.43</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>81.11</v>
+        <v>65.80000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[1, 0, 4, 7, 3]</t>
+          <t>[3, 6, 4, 4, 8]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9765678609365428</v>
+        <v>0.9431745669303903</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9765678609365428</v>
+        <v>0.9431745669303903</v>
       </c>
       <c r="E8" t="n">
-        <v>114.46</v>
+        <v>104.25</v>
       </c>
       <c r="F8" t="n">
-        <v>94.67999999999999</v>
+        <v>65.78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[4, 6, 6, 4, 7]</t>
+          <t>[9, 7, 4, 4, 7]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9731103863613442</v>
+        <v>0.9428283132834516</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9731103863613442</v>
+        <v>0.9428283132834516</v>
       </c>
       <c r="E9" t="n">
-        <v>113.7</v>
+        <v>108.36</v>
       </c>
       <c r="F9" t="n">
-        <v>91.98999999999999</v>
+        <v>90.38999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[1, 8, 4, 3, 6]</t>
+          <t>[7, 1, 4, 5, 7]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9738859519171408</v>
+        <v>0.9730419035230796</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9738859519171408</v>
+        <v>0.9730419035230796</v>
       </c>
       <c r="E10" t="n">
-        <v>101.45</v>
+        <v>113.18</v>
       </c>
       <c r="F10" t="n">
-        <v>79.21000000000001</v>
+        <v>98.46000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[4, 5, 1, 2, 7]</t>
+          <t>[6, 6, 0, 3, 1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 3]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9594142871298563</v>
+        <v>0.9552070749255496</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9594142871298563</v>
+        <v>0.9552070749255496</v>
       </c>
       <c r="E11" t="n">
-        <v>102.26</v>
+        <v>118.66</v>
       </c>
       <c r="F11" t="n">
-        <v>94.44</v>
+        <v>82.33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[5, 2, 8, 3, 7]</t>
+          <t>[7, 7, 6, 7, 1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 3]</t>
+          <t>[2, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9523306430054703</v>
+        <v>0.9684409235506507</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9523306430054703</v>
+        <v>0.9684409235506507</v>
       </c>
       <c r="E12" t="n">
-        <v>106.04</v>
+        <v>114.74</v>
       </c>
       <c r="F12" t="n">
-        <v>91.49000000000001</v>
+        <v>98.84999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[7, 1, 2, 4, 5]</t>
+          <t>[4, 1, 7, 6, 8]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 2]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9737958141154368</v>
+        <v>0.9514275582821544</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9737958141154368</v>
+        <v>0.9514275582821544</v>
       </c>
       <c r="E13" t="n">
-        <v>107.23</v>
+        <v>119.76</v>
       </c>
       <c r="F13" t="n">
-        <v>99.03</v>
+        <v>96.04999999999998</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[0, 0, 1, 9, 3]</t>
+          <t>[8, 9, 9, 2, 6]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9717160518164516</v>
+        <v>0.934672379281877</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9717160518164516</v>
+        <v>0.934672379281877</v>
       </c>
       <c r="E14" t="n">
-        <v>110.99</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>90.24000000000001</v>
+        <v>70.79000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[5, 4, 6, 1, 6]</t>
+          <t>[3, 7, 0, 6, 6]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[2, 2, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9923932205645092</v>
+        <v>0.9650587899785771</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9923932205645092</v>
+        <v>0.9650587899785771</v>
       </c>
       <c r="E15" t="n">
-        <v>107.92</v>
+        <v>118.76</v>
       </c>
       <c r="F15" t="n">
-        <v>97.78</v>
+        <v>79.65000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[6, 6, 4, 7, 1]</t>
+          <t>[9, 7, 0, 9, 0]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9722693636806805</v>
+        <v>0.947275305320226</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9722693636806805</v>
+        <v>0.947275305320226</v>
       </c>
       <c r="E16" t="n">
-        <v>110.16</v>
+        <v>111.78</v>
       </c>
       <c r="F16" t="n">
-        <v>96.25</v>
+        <v>98.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[2, 9, 1, 7, 3]</t>
+          <t>[2, 9, 1, 0, 9]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9733494018449049</v>
+        <v>0.976198055468555</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9733494018449049</v>
+        <v>0.976198055468555</v>
       </c>
       <c r="E17" t="n">
-        <v>101.72</v>
+        <v>118.19</v>
       </c>
       <c r="F17" t="n">
-        <v>86.30000000000001</v>
+        <v>92.03999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[2, 6, 0, 3, 1]</t>
+          <t>[8, 7, 2, 1, 1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9764428128616288</v>
+        <v>0.9701800826410651</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9764428128616288</v>
+        <v>0.9701800826410651</v>
       </c>
       <c r="E18" t="n">
-        <v>107.06</v>
+        <v>105.76</v>
       </c>
       <c r="F18" t="n">
-        <v>87.27000000000001</v>
+        <v>81.93000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[4, 7, 4, 7, 6]</t>
+          <t>[0, 0, 3, 7, 2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 3, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9923452239051341</v>
+        <v>0.9772835573813341</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9923452239051341</v>
+        <v>0.9772835573813341</v>
       </c>
       <c r="E19" t="n">
-        <v>118.5</v>
+        <v>119.84</v>
       </c>
       <c r="F19" t="n">
-        <v>98.76000000000001</v>
+        <v>84.64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 9]</t>
+          <t>[6, 6, 8, 7, 1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9772492032617025</v>
+        <v>0.9613963087763759</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9772492032617025</v>
+        <v>0.9613963087763759</v>
       </c>
       <c r="E20" t="n">
-        <v>100.33</v>
+        <v>106.89</v>
       </c>
       <c r="F20" t="n">
-        <v>94.23</v>
+        <v>80.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[7, 2, 4, 0, 0]</t>
+          <t>[2, 8, 1, 1, 7]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9548986699772187</v>
+        <v>0.9779663089944685</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9548986699772187</v>
+        <v>0.9779663089944685</v>
       </c>
       <c r="E21" t="n">
-        <v>95.65000000000001</v>
+        <v>116.39</v>
       </c>
       <c r="F21" t="n">
-        <v>73.86</v>
+        <v>95.37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[3, 9, 7, 6, 0]</t>
+          <t>[0, 7, 5, 6, 5]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 2, 2]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9882073186698486</v>
+        <v>0.9756991672389418</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9882073186698486</v>
+        <v>0.9756991672389418</v>
       </c>
       <c r="E22" t="n">
-        <v>118.84</v>
+        <v>118.65</v>
       </c>
       <c r="F22" t="n">
-        <v>93.31999999999999</v>
+        <v>86.62</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[7, 8, 7, 6, 3]</t>
+          <t>[0, 5, 6, 0, 1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 2]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9708538233749379</v>
+        <v>0.9765571749272104</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9708538233749379</v>
+        <v>0.9765571749272104</v>
       </c>
       <c r="E23" t="n">
-        <v>118.25</v>
+        <v>113.41</v>
       </c>
       <c r="F23" t="n">
-        <v>96.64</v>
+        <v>82.02</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[0, 1, 7, 7, 1]</t>
+          <t>[1, 1, 0, 6, 1]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 2]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.975188238871066</v>
+        <v>0.974709534018841</v>
       </c>
       <c r="D24" t="n">
-        <v>0.975188238871066</v>
+        <v>0.974709534018841</v>
       </c>
       <c r="E24" t="n">
-        <v>105.76</v>
+        <v>112.69</v>
       </c>
       <c r="F24" t="n">
-        <v>97.03</v>
+        <v>87.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[8, 5, 5, 8, 4]</t>
+          <t>[8, 8, 8, 4, 5]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9674950177337446</v>
+        <v>0.9409545360064733</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9674950177337446</v>
+        <v>0.9409545360064733</v>
       </c>
       <c r="E25" t="n">
-        <v>108.28</v>
+        <v>111.68</v>
       </c>
       <c r="F25" t="n">
-        <v>99.20999999999998</v>
+        <v>85.02</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[7, 8, 6, 4, 3]</t>
+          <t>[2, 0, 3, 3, 6]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[2, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9900671421578395</v>
+        <v>0.9577875159003102</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9900671421578395</v>
+        <v>0.9577875159003102</v>
       </c>
       <c r="E26" t="n">
-        <v>116.19</v>
+        <v>107.32</v>
       </c>
       <c r="F26" t="n">
-        <v>89.29000000000001</v>
+        <v>61.93</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[0, 5, 9, 5, 4]</t>
+          <t>[8, 6, 8, 7, 9]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9681880126334756</v>
+        <v>0.9321108879941491</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9681880126334756</v>
+        <v>0.9321108879941491</v>
       </c>
       <c r="E27" t="n">
-        <v>106.84</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>89.88</v>
+        <v>71.69999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[7, 1, 6, 9, 5]</t>
+          <t>[9, 1, 1, 0, 8]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9449843134623654</v>
+        <v>0.9785225670235228</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9449843134623654</v>
+        <v>0.9785225670235228</v>
       </c>
       <c r="E28" t="n">
-        <v>75.67</v>
+        <v>107.87</v>
       </c>
       <c r="F28" t="n">
-        <v>70.49000000000001</v>
+        <v>94.53999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[4, 6, 5, 6, 9]</t>
+          <t>[9, 9, 5, 5, 0]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9749529198937793</v>
+        <v>0.9589425668829091</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9749529198937793</v>
+        <v>0.9589425668829091</v>
       </c>
       <c r="E29" t="n">
-        <v>115.29</v>
+        <v>104.96</v>
       </c>
       <c r="F29" t="n">
-        <v>97.38000000000001</v>
+        <v>90.09999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[9, 8, 5, 5, 5]</t>
+          <t>[6, 9, 0, 7, 3]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.961534424302402</v>
+        <v>0.9728135506655482</v>
       </c>
       <c r="D30" t="n">
-        <v>0.961534424302402</v>
+        <v>0.9728135506655482</v>
       </c>
       <c r="E30" t="n">
-        <v>97.70999999999999</v>
+        <v>109.15</v>
       </c>
       <c r="F30" t="n">
-        <v>87.09</v>
+        <v>87.92999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[5, 1, 0, 8, 5]</t>
+          <t>[6, 8, 8, 1, 8]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 3, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9718396897403527</v>
+        <v>0.9656934793004199</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9718396897403527</v>
+        <v>0.9656934793004199</v>
       </c>
       <c r="E31" t="n">
-        <v>95.78</v>
+        <v>111.02</v>
       </c>
       <c r="F31" t="n">
-        <v>89.21000000000001</v>
+        <v>93.86999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[3, 3, 9, 4, 4]</t>
+          <t>[8, 8, 0, 8, 7]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 2]</t>
+          <t>[3, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9745671731700105</v>
+        <v>0.9648684156740475</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9745671731700105</v>
+        <v>0.9648684156740475</v>
       </c>
       <c r="E32" t="n">
-        <v>118.43</v>
+        <v>107.32</v>
       </c>
       <c r="F32" t="n">
-        <v>89.19</v>
+        <v>97.69999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[7, 0, 7, 9, 5]</t>
+          <t>[9, 8, 2, 9, 0]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.969188258125645</v>
+        <v>0.959787373739092</v>
       </c>
       <c r="D33" t="n">
-        <v>0.969188258125645</v>
+        <v>0.959787373739092</v>
       </c>
       <c r="E33" t="n">
-        <v>91.41</v>
+        <v>117.13</v>
       </c>
       <c r="F33" t="n">
-        <v>80.59999999999999</v>
+        <v>84.02</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[8, 1, 9, 3, 4]</t>
+          <t>[5, 8, 1, 3, 7]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9641273305420084</v>
+        <v>0.9659817616521471</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9641273305420084</v>
+        <v>0.9659817616521471</v>
       </c>
       <c r="E34" t="n">
-        <v>119.64</v>
+        <v>101.81</v>
       </c>
       <c r="F34" t="n">
-        <v>92.58000000000001</v>
+        <v>79.98</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[8, 7, 6, 4, 4]</t>
+          <t>[2, 3, 0, 2, 3]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1264,400 +1264,400 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9431100646598884</v>
+        <v>0.9602630596930221</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9431100646598884</v>
+        <v>0.9602630596930221</v>
       </c>
       <c r="E35" t="n">
-        <v>84.77000000000001</v>
+        <v>110.03</v>
       </c>
       <c r="F35" t="n">
-        <v>65.29000000000001</v>
+        <v>59.05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[9, 9, 3, 5, 7]</t>
+          <t>[8, 6, 2, 8, 8]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9634507074072963</v>
+        <v>0.9614882039598404</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9634507074072963</v>
+        <v>0.9614882039598404</v>
       </c>
       <c r="E36" t="n">
-        <v>97.75999999999999</v>
+        <v>109.22</v>
       </c>
       <c r="F36" t="n">
-        <v>83.84999999999998</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[4, 2, 3, 4, 2]</t>
+          <t>[1, 4, 6, 1, 8]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9738322841271023</v>
+        <v>0.9713125079942186</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9738322841271023</v>
+        <v>0.9713125079942186</v>
       </c>
       <c r="E37" t="n">
-        <v>108.27</v>
+        <v>112.65</v>
       </c>
       <c r="F37" t="n">
-        <v>84.59999999999999</v>
+        <v>84.00999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[7, 6, 0, 6, 9]</t>
+          <t>[5, 0, 5, 1, 7]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 2, 1, 2]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9717881748570362</v>
+        <v>0.9805226017368043</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9717881748570362</v>
+        <v>0.9805226017368043</v>
       </c>
       <c r="E38" t="n">
-        <v>104.18</v>
+        <v>110.86</v>
       </c>
       <c r="F38" t="n">
-        <v>83.89</v>
+        <v>91.47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[6, 5, 7, 1, 3]</t>
+          <t>[6, 9, 7, 0, 5]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 2, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9922579710506689</v>
+        <v>0.9694327884876325</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9922579710506689</v>
+        <v>0.9694327884876325</v>
       </c>
       <c r="E39" t="n">
-        <v>99.78</v>
+        <v>107.6</v>
       </c>
       <c r="F39" t="n">
-        <v>93.50000000000001</v>
+        <v>83.79000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[7, 9, 8, 5, 6]</t>
+          <t>[8, 4, 5, 0, 5]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 2]</t>
+          <t>[3, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9652211156001111</v>
+        <v>0.9777055598254426</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9652211156001111</v>
+        <v>0.9777055598254426</v>
       </c>
       <c r="E40" t="n">
-        <v>110.26</v>
+        <v>117.22</v>
       </c>
       <c r="F40" t="n">
-        <v>94.18000000000001</v>
+        <v>90.81999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[0, 8, 8, 3, 1]</t>
+          <t>[1, 9, 4, 2, 8]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9684344050066056</v>
+        <v>0.9535175493876892</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9684344050066056</v>
+        <v>0.9535175493876892</v>
       </c>
       <c r="E41" t="n">
-        <v>116.34</v>
+        <v>112.15</v>
       </c>
       <c r="F41" t="n">
-        <v>85.36000000000001</v>
+        <v>82.77</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[1, 8, 5, 8, 5]</t>
+          <t>[0, 3, 5, 7, 9]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9624775234118754</v>
+        <v>0.9910694005061051</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9624775234118754</v>
+        <v>0.9910694005061051</v>
       </c>
       <c r="E42" t="n">
-        <v>93.81</v>
+        <v>118.59</v>
       </c>
       <c r="F42" t="n">
-        <v>87.09999999999999</v>
+        <v>96.18000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[3, 3, 4, 2, 5]</t>
+          <t>[1, 6, 7, 8, 7]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9729693876042382</v>
+        <v>0.9481195397760553</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9729693876042382</v>
+        <v>0.9481195397760553</v>
       </c>
       <c r="E43" t="n">
-        <v>101.25</v>
+        <v>109.3</v>
       </c>
       <c r="F43" t="n">
-        <v>84.47</v>
+        <v>99.82999999999998</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[6, 1, 7, 4, 8]</t>
+          <t>[3, 6, 6, 5, 7]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1]</t>
+          <t>[1, 1, 1, 2, 2]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.970172149940454</v>
+        <v>0.9682594435989124</v>
       </c>
       <c r="D44" t="n">
-        <v>0.970172149940454</v>
+        <v>0.9682594435989124</v>
       </c>
       <c r="E44" t="n">
-        <v>117.49</v>
+        <v>119.95</v>
       </c>
       <c r="F44" t="n">
-        <v>93.81999999999999</v>
+        <v>87.02000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[2, 3, 0, 7, 0]</t>
+          <t>[1, 3, 6, 8, 1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9716030760851949</v>
+        <v>0.9509127074745147</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9716030760851949</v>
+        <v>0.9509127074745147</v>
       </c>
       <c r="E45" t="n">
-        <v>113.95</v>
+        <v>111.05</v>
       </c>
       <c r="F45" t="n">
-        <v>89.24000000000001</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[1, 3, 0, 7, 6]</t>
+          <t>[4, 9, 1, 4, 5]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9714724063508187</v>
+        <v>0.9448667862803648</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9714724063508187</v>
+        <v>0.9448667862803648</v>
       </c>
       <c r="E46" t="n">
-        <v>97.97</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>83.69</v>
+        <v>70.92999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[4, 4, 9, 8, 6]</t>
+          <t>[5, 0, 1, 3, 6]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9653486111853019</v>
+        <v>0.9770351458076018</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9653486111853019</v>
+        <v>0.9770351458076018</v>
       </c>
       <c r="E47" t="n">
-        <v>110.71</v>
+        <v>110</v>
       </c>
       <c r="F47" t="n">
-        <v>84.7</v>
+        <v>75.83000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[4, 4, 1, 5, 0]</t>
+          <t>[9, 6, 0, 5, 7]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9800672474015355</v>
+        <v>0.9639332883925369</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9800672474015355</v>
+        <v>0.9639332883925369</v>
       </c>
       <c r="E48" t="n">
-        <v>115.02</v>
+        <v>105.99</v>
       </c>
       <c r="F48" t="n">
-        <v>99.84999999999999</v>
+        <v>89.21000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[7, 1, 4, 0, 1]</t>
+          <t>[6, 6, 5, 8, 8]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[2, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9811365408300138</v>
+        <v>0.9674379867328594</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9811365408300138</v>
+        <v>0.9674379867328594</v>
       </c>
       <c r="E49" t="n">
-        <v>118.12</v>
+        <v>118.68</v>
       </c>
       <c r="F49" t="n">
-        <v>97.80000000000001</v>
+        <v>84.42999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[8, 1, 6, 3, 6]</t>
+          <t>[2, 9, 1, 1, 1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 2, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.992011662280495</v>
+        <v>0.9583371205805238</v>
       </c>
       <c r="D50" t="n">
-        <v>0.992011662280495</v>
+        <v>0.9583371205805238</v>
       </c>
       <c r="E50" t="n">
-        <v>117.19</v>
+        <v>113.54</v>
       </c>
       <c r="F50" t="n">
-        <v>93.32000000000001</v>
+        <v>86.28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[6, 3, 5, 0, 3]</t>
+          <t>[2, 0, 8, 7, 9]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 3]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9571074918667767</v>
+        <v>0.9744871082231858</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9571074918667767</v>
+        <v>0.9744871082231858</v>
       </c>
       <c r="E51" t="n">
-        <v>114.23</v>
+        <v>112.87</v>
       </c>
       <c r="F51" t="n">
-        <v>90.31</v>
+        <v>81.06999999999999</v>
       </c>
     </row>
   </sheetData>
